--- a/Analysis/exports/fundamental_screener_20261004.xlsx
+++ b/Analysis/exports/fundamental_screener_20261004.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/I325211/Local_Project/Analysis/exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EB7F52-C1BC-9B46-9769-1F0537E3FE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE785469-3C4E-C648-B520-950EBC5C44EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3359,4070 +3359,4070 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
-        <v>26</v>
+      <c r="A2" s="19" t="s">
+        <v>48</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D2" s="5">
-        <v>1159.8</v>
+        <v>16.329999999999998</v>
       </c>
       <c r="E2" s="6">
-        <v>12.4</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="F2" s="5">
-        <v>597.73</v>
+        <v>21.06</v>
       </c>
       <c r="G2" s="5">
-        <v>372.78</v>
+        <v>16.93</v>
       </c>
       <c r="H2" s="5">
-        <v>273.73</v>
+        <v>12.57</v>
       </c>
       <c r="I2" s="5">
-        <v>124.24</v>
+        <v>14.82</v>
       </c>
       <c r="J2" s="7">
-        <v>60.3</v>
+        <v>24.4</v>
       </c>
       <c r="K2" s="7">
-        <v>36.200000000000003</v>
+        <v>34.6</v>
       </c>
       <c r="L2" s="8">
-        <v>20270.900000000001</v>
+        <v>268.89999999999998</v>
       </c>
       <c r="M2" s="5">
-        <v>1077.01</v>
+        <v>15.74</v>
       </c>
       <c r="N2" s="15">
-        <v>-62.94</v>
-      </c>
-      <c r="O2">
-        <v>4</v>
+        <v>-16.07</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>29</v>
+        <v>157</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>30</v>
+        <v>158</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D3" s="11">
-        <v>2679.7</v>
+        <v>7.9</v>
       </c>
       <c r="E3" s="12">
-        <v>14.2</v>
+        <v>31.6</v>
       </c>
       <c r="F3" s="11">
-        <v>641.24</v>
+        <v>42.32</v>
       </c>
       <c r="G3" s="11">
-        <v>536.30999999999995</v>
+        <v>33.229999999999997</v>
       </c>
       <c r="H3" s="11">
-        <v>457.09</v>
+        <v>18.53</v>
       </c>
       <c r="I3" s="11">
-        <v>376.26</v>
+        <v>14.52</v>
       </c>
       <c r="J3" s="7">
-        <v>19.600000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="K3" s="7">
-        <v>17.3</v>
+        <v>79.3</v>
       </c>
       <c r="L3" s="13">
-        <v>19854.3</v>
+        <v>338.8</v>
       </c>
       <c r="M3" s="11">
-        <v>2288.77</v>
-      </c>
-      <c r="N3" s="15">
-        <v>-33.869999999999997</v>
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="N3" s="9">
+        <v>4.8499999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="5">
-        <v>609.75</v>
-      </c>
-      <c r="E4" s="6">
-        <v>14.5</v>
-      </c>
-      <c r="F4" s="5">
-        <v>297.32</v>
-      </c>
-      <c r="G4" s="5">
-        <v>247.62</v>
-      </c>
-      <c r="H4" s="5">
-        <v>173.77</v>
-      </c>
-      <c r="I4" s="5">
-        <v>122.95</v>
+      <c r="D4" s="11">
+        <v>280.8</v>
+      </c>
+      <c r="E4" s="12">
+        <v>28.2</v>
+      </c>
+      <c r="F4" s="11">
+        <v>19.3</v>
+      </c>
+      <c r="G4" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="H4" s="11">
+        <v>10.02</v>
+      </c>
+      <c r="I4" s="11">
+        <v>2.88</v>
       </c>
       <c r="J4" s="7">
-        <v>20.100000000000001</v>
+        <v>50.8</v>
       </c>
       <c r="K4" s="7">
-        <v>42.5</v>
-      </c>
-      <c r="L4" s="8">
-        <v>12183.4</v>
-      </c>
-      <c r="M4" s="5">
-        <v>524.4</v>
-      </c>
-      <c r="N4" s="15">
-        <v>-32.78</v>
-      </c>
-      <c r="O4">
-        <v>10</v>
+        <v>27.7</v>
+      </c>
+      <c r="L4" s="13">
+        <v>448.6</v>
+      </c>
+      <c r="M4" s="11">
+        <v>293.79000000000002</v>
+      </c>
+      <c r="N4" s="9">
+        <v>1.69</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
-        <v>35</v>
+      <c r="A5" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="11">
+        <v>15.78</v>
+      </c>
+      <c r="E5" s="12">
+        <v>22.1</v>
+      </c>
+      <c r="F5" s="11">
+        <v>45.22</v>
+      </c>
+      <c r="G5" s="11">
+        <v>23.1</v>
+      </c>
+      <c r="H5" s="11">
+        <v>20.21</v>
+      </c>
+      <c r="I5" s="11">
+        <v>12.7</v>
+      </c>
+      <c r="J5" s="7">
+        <v>95.8</v>
+      </c>
+      <c r="K5" s="7">
+        <v>14.3</v>
+      </c>
+      <c r="L5" s="13">
+        <v>516.70000000000005</v>
+      </c>
+      <c r="M5" s="11">
+        <v>14.92</v>
+      </c>
+      <c r="N5" s="15">
+        <v>-8.3699999999999992</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="5">
+        <v>141.35</v>
+      </c>
+      <c r="E6" s="6">
+        <v>21.5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>45.36</v>
+      </c>
+      <c r="G6" s="5">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="H6" s="5">
+        <v>31.18</v>
+      </c>
+      <c r="I6" s="5">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="J6" s="7">
+        <v>20</v>
+      </c>
+      <c r="K6" s="7">
+        <v>21.2</v>
+      </c>
+      <c r="L6" s="8">
+        <v>701.8</v>
+      </c>
+      <c r="M6" s="5">
+        <v>128.77000000000001</v>
+      </c>
+      <c r="N6" s="15">
+        <v>-8.3699999999999992</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="11">
-        <v>695.55</v>
-      </c>
-      <c r="E5" s="12">
-        <v>14.6</v>
-      </c>
-      <c r="F5" s="11">
-        <v>142.27000000000001</v>
-      </c>
-      <c r="G5" s="11">
-        <v>126.64</v>
-      </c>
-      <c r="H5" s="11">
-        <v>101.1</v>
-      </c>
-      <c r="I5" s="11">
-        <v>136.56</v>
-      </c>
-      <c r="J5" s="7">
-        <v>12.3</v>
-      </c>
-      <c r="K5" s="7">
-        <v>25.3</v>
-      </c>
-      <c r="L5" s="13">
-        <v>4429.3</v>
-      </c>
-      <c r="M5" s="11">
-        <v>596.47</v>
-      </c>
-      <c r="N5" s="15">
-        <v>-25.79</v>
-      </c>
-      <c r="O5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1135.5999999999999</v>
-      </c>
-      <c r="E6" s="6">
-        <v>14.8</v>
-      </c>
-      <c r="F6" s="5">
-        <v>3428.2</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2764.3</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1549.1</v>
-      </c>
-      <c r="I6" s="5">
-        <v>486.7</v>
-      </c>
-      <c r="J6" s="7">
-        <v>24</v>
-      </c>
-      <c r="K6" s="7">
-        <v>78.400000000000006</v>
-      </c>
-      <c r="L6" s="8">
-        <v>110474.1</v>
-      </c>
-      <c r="M6" s="5">
-        <v>1074.97</v>
-      </c>
-      <c r="N6" s="15">
-        <v>-23.55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>34</v>
-      </c>
       <c r="D7" s="11">
-        <v>786.4</v>
+        <v>124.37</v>
       </c>
       <c r="E7" s="12">
-        <v>15</v>
+        <v>38.5</v>
       </c>
       <c r="F7" s="11">
-        <v>351.66</v>
+        <v>38.840000000000003</v>
       </c>
       <c r="G7" s="11">
-        <v>322.41000000000003</v>
+        <v>31.74</v>
       </c>
       <c r="H7" s="11">
-        <v>251.33</v>
+        <v>18.3</v>
       </c>
       <c r="I7" s="11">
-        <v>248.79</v>
+        <v>10.34</v>
       </c>
       <c r="J7" s="7">
-        <v>9.1</v>
+        <v>22.4</v>
       </c>
       <c r="K7" s="7">
-        <v>28.3</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="L7" s="13">
-        <v>5175.8</v>
+        <v>739.9</v>
       </c>
       <c r="M7" s="11">
-        <v>701.31</v>
-      </c>
-      <c r="N7" s="15">
-        <v>-18.920000000000002</v>
+        <v>141</v>
+      </c>
+      <c r="N7" s="14">
+        <v>15.54</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="A8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="5">
-        <v>1946.9</v>
-      </c>
-      <c r="E8" s="6">
-        <v>15.5</v>
-      </c>
-      <c r="F8" s="5">
-        <v>51.72</v>
-      </c>
-      <c r="G8" s="5">
-        <v>30.93</v>
-      </c>
-      <c r="H8" s="5">
-        <v>21.88</v>
-      </c>
-      <c r="I8" s="5">
-        <v>8.44</v>
+      <c r="D8" s="11">
+        <v>676.55</v>
+      </c>
+      <c r="E8" s="12">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F8" s="11">
+        <v>28.74</v>
+      </c>
+      <c r="G8" s="11">
+        <v>10.96</v>
+      </c>
+      <c r="H8" s="11">
+        <v>3.31</v>
+      </c>
+      <c r="I8" s="11">
+        <v>7.85</v>
       </c>
       <c r="J8" s="7">
-        <v>67.2</v>
+        <v>162.19999999999999</v>
       </c>
       <c r="K8" s="7">
-        <v>41.4</v>
-      </c>
-      <c r="L8" s="8">
-        <v>2032.4</v>
-      </c>
-      <c r="M8" s="5">
-        <v>1933.4</v>
+        <v>231.6</v>
+      </c>
+      <c r="L8" s="13">
+        <v>767.9</v>
+      </c>
+      <c r="M8" s="11">
+        <v>709.12</v>
       </c>
       <c r="N8" s="15">
-        <v>-16.41</v>
-      </c>
-      <c r="O8">
-        <v>3</v>
+        <v>-14.18</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>45</v>
+        <v>191</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D9" s="11">
-        <v>662.15</v>
+        <v>167.92</v>
       </c>
       <c r="E9" s="12">
-        <v>16</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="F9" s="11">
-        <v>127.66</v>
+        <v>107.15</v>
       </c>
       <c r="G9" s="11">
-        <v>80.989999999999995</v>
+        <v>24.79</v>
       </c>
       <c r="H9" s="11">
-        <v>78.58</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="I9" s="11">
-        <v>18.41</v>
+        <v>45.18</v>
       </c>
       <c r="J9" s="7">
-        <v>57.6</v>
+        <v>332.3</v>
       </c>
       <c r="K9" s="7">
-        <v>3.1</v>
+        <v>39.6</v>
       </c>
       <c r="L9" s="13">
-        <v>4163.8999999999996</v>
+        <v>1002.4</v>
       </c>
       <c r="M9" s="11">
-        <v>563.22</v>
-      </c>
-      <c r="N9" s="15">
-        <v>-16.29</v>
+        <v>173.82</v>
+      </c>
+      <c r="N9" s="14">
+        <v>12.13</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="A10" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="5">
-        <v>16.329999999999998</v>
-      </c>
-      <c r="E10" s="6">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="F10" s="5">
-        <v>21.06</v>
-      </c>
-      <c r="G10" s="5">
-        <v>16.93</v>
-      </c>
-      <c r="H10" s="5">
-        <v>12.57</v>
-      </c>
-      <c r="I10" s="5">
-        <v>14.82</v>
+      <c r="D10" s="11">
+        <v>58.25</v>
+      </c>
+      <c r="E10" s="12">
+        <v>20.8</v>
+      </c>
+      <c r="F10" s="11">
+        <v>98.23</v>
+      </c>
+      <c r="G10" s="11">
+        <v>54.67</v>
+      </c>
+      <c r="H10" s="11">
+        <v>14.21</v>
+      </c>
+      <c r="I10" s="11">
+        <v>5.79</v>
       </c>
       <c r="J10" s="7">
-        <v>24.4</v>
+        <v>79.7</v>
       </c>
       <c r="K10" s="7">
-        <v>34.6</v>
-      </c>
-      <c r="L10" s="8">
-        <v>268.89999999999998</v>
-      </c>
-      <c r="M10" s="5">
-        <v>15.74</v>
+        <v>284.8</v>
+      </c>
+      <c r="L10" s="13">
+        <v>1107.0999999999999</v>
+      </c>
+      <c r="M10" s="11">
+        <v>57.95</v>
       </c>
       <c r="N10" s="15">
-        <v>-16.07</v>
+        <v>-9.06</v>
+      </c>
+      <c r="O10">
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="11">
-        <v>577.4</v>
-      </c>
-      <c r="E11" s="12">
-        <v>16.3</v>
-      </c>
-      <c r="F11" s="11">
-        <v>77.510000000000005</v>
-      </c>
-      <c r="G11" s="11">
-        <v>66.75</v>
-      </c>
-      <c r="H11" s="11">
-        <v>48.81</v>
-      </c>
-      <c r="I11" s="11">
-        <v>48.17</v>
+      <c r="A11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="5">
+        <v>566.6</v>
+      </c>
+      <c r="E11" s="6">
+        <v>28.7</v>
+      </c>
+      <c r="F11" s="5">
+        <v>100.84</v>
+      </c>
+      <c r="G11" s="5">
+        <v>66.47</v>
+      </c>
+      <c r="H11" s="5">
+        <v>42.75</v>
+      </c>
+      <c r="I11" s="5">
+        <v>90.32</v>
       </c>
       <c r="J11" s="7">
-        <v>16.100000000000001</v>
+        <v>51.7</v>
       </c>
       <c r="K11" s="7">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="L11" s="13">
-        <v>2637.3</v>
-      </c>
-      <c r="M11" s="11">
-        <v>577.5</v>
-      </c>
-      <c r="N11" s="15">
-        <v>-14.75</v>
-      </c>
-      <c r="O11">
-        <v>8</v>
+        <v>55.5</v>
+      </c>
+      <c r="L11" s="8">
+        <v>1170.0999999999999</v>
+      </c>
+      <c r="M11" s="5">
+        <v>508.39</v>
+      </c>
+      <c r="N11" s="9">
+        <v>2.46</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="5">
-        <v>210.95</v>
-      </c>
-      <c r="E12" s="6">
-        <v>16.3</v>
-      </c>
-      <c r="F12" s="5">
-        <v>369.38</v>
-      </c>
-      <c r="G12" s="5">
-        <v>245.58</v>
-      </c>
-      <c r="H12" s="5">
-        <v>135.76</v>
-      </c>
-      <c r="I12" s="5">
-        <v>132.41</v>
+      <c r="A12" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="11">
+        <v>427.5</v>
+      </c>
+      <c r="E12" s="12">
+        <v>31.7</v>
+      </c>
+      <c r="F12" s="11">
+        <v>42.26</v>
+      </c>
+      <c r="G12" s="11">
+        <v>21.63</v>
+      </c>
+      <c r="H12" s="11">
+        <v>8.98</v>
+      </c>
+      <c r="I12" s="11">
+        <v>4</v>
       </c>
       <c r="J12" s="7">
-        <v>50.4</v>
+        <v>95.4</v>
       </c>
       <c r="K12" s="7">
-        <v>80.900000000000006</v>
-      </c>
-      <c r="L12" s="8">
-        <v>6226.3</v>
-      </c>
-      <c r="M12" s="5">
-        <v>213.11</v>
-      </c>
-      <c r="N12" s="15">
-        <v>-14.46</v>
+        <v>140.9</v>
+      </c>
+      <c r="L12" s="13">
+        <v>1176.7</v>
+      </c>
+      <c r="M12" s="11">
+        <v>468.5</v>
+      </c>
+      <c r="N12" s="9">
+        <v>5.41</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>55</v>
+        <v>203</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="D13" s="11">
-        <v>676.55</v>
+        <v>1013.05</v>
       </c>
       <c r="E13" s="12">
-        <v>16.600000000000001</v>
+        <v>38</v>
       </c>
       <c r="F13" s="11">
-        <v>28.74</v>
+        <v>84.74</v>
       </c>
       <c r="G13" s="11">
-        <v>10.96</v>
+        <v>72.39</v>
       </c>
       <c r="H13" s="11">
-        <v>3.31</v>
+        <v>53.83</v>
       </c>
       <c r="I13" s="11">
-        <v>7.85</v>
+        <v>33.450000000000003</v>
       </c>
       <c r="J13" s="7">
-        <v>162.19999999999999</v>
+        <v>17</v>
       </c>
       <c r="K13" s="7">
-        <v>231.6</v>
+        <v>34.5</v>
       </c>
       <c r="L13" s="13">
-        <v>767.9</v>
+        <v>1203.7</v>
       </c>
       <c r="M13" s="11">
-        <v>709.12</v>
-      </c>
-      <c r="N13" s="15">
-        <v>-14.18</v>
+        <v>1122.68</v>
+      </c>
+      <c r="N13" s="14">
+        <v>13.44</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18" t="s">
-        <v>57</v>
+      <c r="A14" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="5">
-        <v>1140.3</v>
+        <v>206.14</v>
       </c>
       <c r="E14" s="6">
-        <v>16.600000000000001</v>
+        <v>30.9</v>
       </c>
       <c r="F14" s="5">
-        <v>591.17999999999995</v>
+        <v>42.23</v>
       </c>
       <c r="G14" s="5">
-        <v>539.1</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="H14" s="5">
-        <v>521.67999999999995</v>
+        <v>25.05</v>
       </c>
       <c r="I14" s="5">
-        <v>494.69</v>
+        <v>21.55</v>
       </c>
       <c r="J14" s="7">
-        <v>9.6999999999999993</v>
+        <v>29.1</v>
       </c>
       <c r="K14" s="7">
-        <v>3.3</v>
+        <v>30.5</v>
       </c>
       <c r="L14" s="8">
-        <v>23723.5</v>
+        <v>1287.4000000000001</v>
       </c>
       <c r="M14" s="5">
-        <v>1010.63</v>
-      </c>
-      <c r="N14" s="15">
-        <v>-14.03</v>
-      </c>
-      <c r="O14">
-        <v>3</v>
+        <v>202.7</v>
+      </c>
+      <c r="N14" s="9">
+        <v>4.53</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="C15" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="11">
+        <v>878.85</v>
+      </c>
+      <c r="E15" s="12">
+        <v>26.3</v>
+      </c>
+      <c r="F15" s="11">
+        <v>123.98</v>
+      </c>
+      <c r="G15" s="11">
+        <v>103.24</v>
+      </c>
+      <c r="H15" s="11">
+        <v>90.44</v>
+      </c>
+      <c r="I15" s="11">
+        <v>133.88999999999999</v>
+      </c>
+      <c r="J15" s="7">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="K15" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="L15" s="13">
+        <v>1320.7</v>
+      </c>
+      <c r="M15" s="11">
+        <v>805.44</v>
+      </c>
+      <c r="N15" s="15">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="11">
+        <v>134.37</v>
+      </c>
+      <c r="E16" s="12">
+        <v>19</v>
+      </c>
+      <c r="F16" s="11">
+        <v>139.66999999999999</v>
+      </c>
+      <c r="G16" s="11">
+        <v>32.909999999999997</v>
+      </c>
+      <c r="H16" s="11">
+        <v>32.21</v>
+      </c>
+      <c r="I16" s="11">
+        <v>37.9</v>
+      </c>
+      <c r="J16" s="7">
+        <v>324.39999999999998</v>
+      </c>
+      <c r="K16" s="7">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L16" s="13">
+        <v>1418.1</v>
+      </c>
+      <c r="M16" s="11">
+        <v>121.69</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-10.98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="5">
+        <v>255.41</v>
+      </c>
+      <c r="E17" s="6">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="F17" s="5">
+        <v>92.64</v>
+      </c>
+      <c r="G17" s="5">
+        <v>77.05</v>
+      </c>
+      <c r="H17" s="5">
+        <v>45.63</v>
+      </c>
+      <c r="I17" s="5">
+        <v>32.89</v>
+      </c>
+      <c r="J17" s="7">
+        <v>20.2</v>
+      </c>
+      <c r="K17" s="7">
+        <v>68.8</v>
+      </c>
+      <c r="L17" s="8">
+        <v>1452.7</v>
+      </c>
+      <c r="M17" s="5">
+        <v>305.10000000000002</v>
+      </c>
+      <c r="N17" s="9">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="11">
+        <v>58.13</v>
+      </c>
+      <c r="E18" s="12">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="F18" s="11">
+        <v>91.7</v>
+      </c>
+      <c r="G18" s="11">
+        <v>77.81</v>
+      </c>
+      <c r="H18" s="11">
+        <v>74.83</v>
+      </c>
+      <c r="I18" s="11">
+        <v>42.84</v>
+      </c>
+      <c r="J18" s="7">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="K18" s="7">
+        <v>4</v>
+      </c>
+      <c r="L18" s="13">
+        <v>1508.8</v>
+      </c>
+      <c r="M18" s="11">
+        <v>71.69</v>
+      </c>
+      <c r="N18" s="14">
+        <v>10.58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="11">
-        <v>491.3</v>
-      </c>
-      <c r="E15" s="12">
-        <v>17.3</v>
-      </c>
-      <c r="F15" s="11">
-        <v>182.58</v>
-      </c>
-      <c r="G15" s="11">
-        <v>165.63</v>
-      </c>
-      <c r="H15" s="11">
-        <v>132.27000000000001</v>
-      </c>
-      <c r="I15" s="11">
-        <v>87.8</v>
-      </c>
-      <c r="J15" s="7">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="K15" s="7">
-        <v>25.2</v>
-      </c>
-      <c r="L15" s="13">
-        <v>4985.8</v>
-      </c>
-      <c r="M15" s="11">
-        <v>452.97</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-13.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="5">
-        <v>246.88</v>
-      </c>
-      <c r="E16" s="6">
-        <v>17.3</v>
-      </c>
-      <c r="F16" s="5">
-        <v>949.15</v>
-      </c>
-      <c r="G16" s="5">
-        <v>478.53</v>
-      </c>
-      <c r="H16" s="5">
-        <v>279.41000000000003</v>
-      </c>
-      <c r="I16" s="5">
-        <v>204.65</v>
-      </c>
-      <c r="J16" s="7">
-        <v>98.3</v>
-      </c>
-      <c r="K16" s="7">
-        <v>71.3</v>
-      </c>
-      <c r="L16" s="8">
-        <v>24055.8</v>
-      </c>
-      <c r="M16" s="5">
-        <v>218.36</v>
-      </c>
-      <c r="N16" s="15">
-        <v>-11.79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+      <c r="D19" s="5">
+        <v>132.6</v>
+      </c>
+      <c r="E19" s="6">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F19" s="5">
+        <v>119.79</v>
+      </c>
+      <c r="G19" s="5">
+        <v>82.18</v>
+      </c>
+      <c r="H19" s="5">
+        <v>60.17</v>
+      </c>
+      <c r="I19" s="5">
+        <v>143.24</v>
+      </c>
+      <c r="J19" s="7">
+        <v>45.8</v>
+      </c>
+      <c r="K19" s="7">
+        <v>36.6</v>
+      </c>
+      <c r="L19" s="8">
+        <v>1511.5</v>
+      </c>
+      <c r="M19" s="5">
+        <v>155.01</v>
+      </c>
+      <c r="N19" s="14">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="11">
+        <v>998.3</v>
+      </c>
+      <c r="E20" s="12">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="F20" s="11">
+        <v>145.72999999999999</v>
+      </c>
+      <c r="G20" s="11">
+        <v>140.91999999999999</v>
+      </c>
+      <c r="H20" s="11">
+        <v>95.51</v>
+      </c>
+      <c r="I20" s="11">
+        <v>124.61</v>
+      </c>
+      <c r="J20" s="7">
+        <v>3.4</v>
+      </c>
+      <c r="K20" s="7">
+        <v>47.5</v>
+      </c>
+      <c r="L20" s="13">
+        <v>1650.8</v>
+      </c>
+      <c r="M20" s="11">
+        <v>1509.5</v>
+      </c>
+      <c r="N20" s="14">
+        <v>16.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="11">
+        <v>704.7</v>
+      </c>
+      <c r="E21" s="12">
+        <v>30.7</v>
+      </c>
+      <c r="F21" s="11">
+        <v>61.94</v>
+      </c>
+      <c r="G21" s="11">
+        <v>53.26</v>
+      </c>
+      <c r="H21" s="11">
+        <v>38.71</v>
+      </c>
+      <c r="I21" s="11">
+        <v>28.11</v>
+      </c>
+      <c r="J21" s="7">
+        <v>16.3</v>
+      </c>
+      <c r="K21" s="7">
+        <v>37.6</v>
+      </c>
+      <c r="L21" s="13">
+        <v>1686.7</v>
+      </c>
+      <c r="M21" s="11">
+        <v>798.19</v>
+      </c>
+      <c r="N21" s="9">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="5">
+        <v>950.25</v>
+      </c>
+      <c r="E22" s="6">
+        <v>24.1</v>
+      </c>
+      <c r="F22" s="5">
+        <v>52.85</v>
+      </c>
+      <c r="G22" s="5">
+        <v>48.36</v>
+      </c>
+      <c r="H22" s="5">
+        <v>40.29</v>
+      </c>
+      <c r="I22" s="5">
+        <v>21.8</v>
+      </c>
+      <c r="J22" s="7">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="K22" s="7">
+        <v>20</v>
+      </c>
+      <c r="L22" s="8">
+        <v>1694.6</v>
+      </c>
+      <c r="M22" s="5">
+        <v>916.54</v>
+      </c>
+      <c r="N22" s="15">
+        <v>-6.02</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B23" s="10" t="s">
         <v>64</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="11">
-        <v>352.3</v>
-      </c>
-      <c r="E17" s="12">
-        <v>17.7</v>
-      </c>
-      <c r="F17" s="11">
-        <v>48.96</v>
-      </c>
-      <c r="G17" s="11">
-        <v>43.4</v>
-      </c>
-      <c r="H17" s="11">
-        <v>36.450000000000003</v>
-      </c>
-      <c r="I17" s="11">
-        <v>37.700000000000003</v>
-      </c>
-      <c r="J17" s="7">
-        <v>12.8</v>
-      </c>
-      <c r="K17" s="7">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="L17" s="13">
-        <v>1743.1</v>
-      </c>
-      <c r="M17" s="11">
-        <v>322.05</v>
-      </c>
-      <c r="N17" s="15">
-        <v>-11.71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="5">
-        <v>659.6</v>
-      </c>
-      <c r="E18" s="6">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="F18" s="5">
-        <v>360.3</v>
-      </c>
-      <c r="G18" s="5">
-        <v>255.4</v>
-      </c>
-      <c r="H18" s="5">
-        <v>227.2</v>
-      </c>
-      <c r="I18" s="5">
-        <v>284.5</v>
-      </c>
-      <c r="J18" s="7">
-        <v>41.1</v>
-      </c>
-      <c r="K18" s="7">
-        <v>12.4</v>
-      </c>
-      <c r="L18" s="8">
-        <v>15640.9</v>
-      </c>
-      <c r="M18" s="5">
-        <v>636.04</v>
-      </c>
-      <c r="N18" s="15">
-        <v>-11.53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="11">
-        <v>134.37</v>
-      </c>
-      <c r="E19" s="12">
-        <v>19</v>
-      </c>
-      <c r="F19" s="11">
-        <v>139.66999999999999</v>
-      </c>
-      <c r="G19" s="11">
-        <v>32.909999999999997</v>
-      </c>
-      <c r="H19" s="11">
-        <v>32.21</v>
-      </c>
-      <c r="I19" s="11">
-        <v>37.9</v>
-      </c>
-      <c r="J19" s="7">
-        <v>324.39999999999998</v>
-      </c>
-      <c r="K19" s="7">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="L19" s="13">
-        <v>1418.1</v>
-      </c>
-      <c r="M19" s="11">
-        <v>121.69</v>
-      </c>
-      <c r="N19" s="15">
-        <v>-10.98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="5">
-        <v>378.9</v>
-      </c>
-      <c r="E20" s="6">
-        <v>19.2</v>
-      </c>
-      <c r="F20" s="5">
-        <v>3764.49</v>
-      </c>
-      <c r="G20" s="5">
-        <v>3304.32</v>
-      </c>
-      <c r="H20" s="5">
-        <v>3284.37</v>
-      </c>
-      <c r="I20" s="5">
-        <v>4795.7700000000004</v>
-      </c>
-      <c r="J20" s="7">
-        <v>13.9</v>
-      </c>
-      <c r="K20" s="7">
-        <v>0.6</v>
-      </c>
-      <c r="L20" s="8">
-        <v>102683.6</v>
-      </c>
-      <c r="M20" s="5">
-        <v>369.79</v>
-      </c>
-      <c r="N20" s="15">
-        <v>-10.97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="11">
-        <v>915.35</v>
-      </c>
-      <c r="E21" s="12">
-        <v>19.8</v>
-      </c>
-      <c r="F21" s="11">
-        <v>209.12</v>
-      </c>
-      <c r="G21" s="11">
-        <v>187.96</v>
-      </c>
-      <c r="H21" s="11">
-        <v>119.11</v>
-      </c>
-      <c r="I21" s="11">
-        <v>89.86</v>
-      </c>
-      <c r="J21" s="7">
-        <v>11.3</v>
-      </c>
-      <c r="K21" s="7">
-        <v>57.8</v>
-      </c>
-      <c r="L21" s="13">
-        <v>7444.7</v>
-      </c>
-      <c r="M21" s="11">
-        <v>812.41</v>
-      </c>
-      <c r="N21" s="15">
-        <v>-10.44</v>
-      </c>
-      <c r="O21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="5">
-        <v>296.5</v>
-      </c>
-      <c r="E22" s="6">
-        <v>20</v>
-      </c>
-      <c r="F22" s="5">
-        <v>1081.55</v>
-      </c>
-      <c r="G22" s="5">
-        <v>369.01</v>
-      </c>
-      <c r="H22" s="5">
-        <v>28.9</v>
-      </c>
-      <c r="I22" s="5">
-        <v>8.94</v>
-      </c>
-      <c r="J22" s="7">
-        <v>193.1</v>
-      </c>
-      <c r="K22" s="7">
-        <v>1176.9000000000001</v>
-      </c>
-      <c r="L22" s="8">
-        <v>21216.9</v>
-      </c>
-      <c r="M22" s="5">
-        <v>287.33999999999997</v>
-      </c>
-      <c r="N22" s="15">
-        <v>-10.02</v>
-      </c>
-      <c r="O22">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D23" s="11">
-        <v>156.76</v>
+        <v>352.3</v>
       </c>
       <c r="E23" s="12">
-        <v>20</v>
+        <v>17.7</v>
       </c>
       <c r="F23" s="11">
-        <v>996.36</v>
+        <v>48.96</v>
       </c>
       <c r="G23" s="11">
-        <v>662.14</v>
+        <v>43.4</v>
       </c>
       <c r="H23" s="11">
-        <v>99.91</v>
+        <v>36.450000000000003</v>
       </c>
       <c r="I23" s="11">
-        <v>304.19</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="J23" s="7">
-        <v>50.5</v>
+        <v>12.8</v>
       </c>
       <c r="K23" s="7">
-        <v>562.70000000000005</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="L23" s="13">
-        <v>15681.7</v>
+        <v>1743.1</v>
       </c>
       <c r="M23" s="11">
-        <v>145.4</v>
+        <v>322.05</v>
       </c>
       <c r="N23" s="15">
-        <v>-9.77</v>
+        <v>-11.71</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="A24" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="5">
-        <v>551.5</v>
-      </c>
-      <c r="E24" s="6">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="F24" s="5">
-        <v>213.13</v>
-      </c>
-      <c r="G24" s="5">
-        <v>149.35</v>
-      </c>
-      <c r="H24" s="5">
-        <v>81.67</v>
-      </c>
-      <c r="I24" s="5">
-        <v>35.57</v>
+      <c r="D24" s="11">
+        <v>95.83</v>
+      </c>
+      <c r="E24" s="12">
+        <v>25.8</v>
+      </c>
+      <c r="F24" s="11">
+        <v>57.65</v>
+      </c>
+      <c r="G24" s="11">
+        <v>40.56</v>
+      </c>
+      <c r="H24" s="11">
+        <v>25.69</v>
+      </c>
+      <c r="I24" s="11">
+        <v>21.5</v>
       </c>
       <c r="J24" s="7">
-        <v>42.7</v>
+        <v>42.2</v>
       </c>
       <c r="K24" s="7">
-        <v>82.9</v>
-      </c>
-      <c r="L24" s="8">
-        <v>6644.3</v>
-      </c>
-      <c r="M24" s="5">
-        <v>505.97</v>
+        <v>57.9</v>
+      </c>
+      <c r="L24" s="13">
+        <v>1924.9</v>
+      </c>
+      <c r="M24" s="11">
+        <v>80.349999999999994</v>
       </c>
       <c r="N24" s="15">
-        <v>-9.7100000000000009</v>
-      </c>
-      <c r="O24">
-        <v>5</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="11">
-        <v>446.05</v>
-      </c>
-      <c r="E25" s="12">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="F25" s="11">
-        <v>84.44</v>
-      </c>
-      <c r="G25" s="11">
-        <v>64.819999999999993</v>
-      </c>
-      <c r="H25" s="11">
-        <v>37.770000000000003</v>
-      </c>
-      <c r="I25" s="11">
-        <v>31.01</v>
+      <c r="A25" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="5">
+        <v>318.95</v>
+      </c>
+      <c r="E25" s="6">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="F25" s="5">
+        <v>292.76</v>
+      </c>
+      <c r="G25" s="5">
+        <v>230.92</v>
+      </c>
+      <c r="H25" s="5">
+        <v>172.99</v>
+      </c>
+      <c r="I25" s="5">
+        <v>125.08</v>
       </c>
       <c r="J25" s="7">
-        <v>30.3</v>
+        <v>26.8</v>
       </c>
       <c r="K25" s="7">
-        <v>71.599999999999994</v>
-      </c>
-      <c r="L25" s="13">
-        <v>2054.6</v>
-      </c>
-      <c r="M25" s="11">
-        <v>388</v>
-      </c>
-      <c r="N25" s="15">
-        <v>-9.1199999999999992</v>
+        <v>33.5</v>
+      </c>
+      <c r="L25" s="8">
+        <v>2004.1</v>
+      </c>
+      <c r="M25" s="5">
+        <v>860.52</v>
+      </c>
+      <c r="N25" s="14">
+        <v>19.27</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="5">
-        <v>526.95000000000005</v>
+        <v>1946.9</v>
       </c>
       <c r="E26" s="6">
-        <v>20.8</v>
+        <v>15.5</v>
       </c>
       <c r="F26" s="5">
-        <v>258.89</v>
+        <v>51.72</v>
       </c>
       <c r="G26" s="5">
-        <v>203.86</v>
+        <v>30.93</v>
       </c>
       <c r="H26" s="5">
-        <v>93.49</v>
+        <v>21.88</v>
       </c>
       <c r="I26" s="5">
-        <v>38.909999999999997</v>
+        <v>8.44</v>
       </c>
       <c r="J26" s="7">
-        <v>27</v>
+        <v>67.2</v>
       </c>
       <c r="K26" s="7">
-        <v>118</v>
+        <v>41.4</v>
       </c>
       <c r="L26" s="8">
-        <v>5936.1</v>
+        <v>2032.4</v>
       </c>
       <c r="M26" s="5">
-        <v>511.86</v>
+        <v>1933.4</v>
       </c>
       <c r="N26" s="15">
-        <v>-9.11</v>
+        <v>-16.41</v>
       </c>
       <c r="O26">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18" t="s">
-        <v>84</v>
+      <c r="A27" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D27" s="11">
-        <v>58.25</v>
+        <v>446.05</v>
       </c>
       <c r="E27" s="12">
-        <v>20.8</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="F27" s="11">
-        <v>98.23</v>
+        <v>84.44</v>
       </c>
       <c r="G27" s="11">
-        <v>54.67</v>
+        <v>64.819999999999993</v>
       </c>
       <c r="H27" s="11">
-        <v>14.21</v>
+        <v>37.770000000000003</v>
       </c>
       <c r="I27" s="11">
+        <v>31.01</v>
+      </c>
+      <c r="J27" s="7">
+        <v>30.3</v>
+      </c>
+      <c r="K27" s="7">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="L27" s="13">
+        <v>2054.6</v>
+      </c>
+      <c r="M27" s="11">
+        <v>388</v>
+      </c>
+      <c r="N27" s="15">
+        <v>-9.1199999999999992</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="11">
+        <v>197.34</v>
+      </c>
+      <c r="E28" s="12">
+        <v>33.1</v>
+      </c>
+      <c r="F28" s="11">
+        <v>92.72</v>
+      </c>
+      <c r="G28" s="11">
+        <v>73.81</v>
+      </c>
+      <c r="H28" s="11">
+        <v>45.98</v>
+      </c>
+      <c r="I28" s="11">
+        <v>19.87</v>
+      </c>
+      <c r="J28" s="7">
+        <v>25.6</v>
+      </c>
+      <c r="K28" s="7">
+        <v>60.5</v>
+      </c>
+      <c r="L28" s="13">
+        <v>2206.1999999999998</v>
+      </c>
+      <c r="M28" s="11">
+        <v>187.21</v>
+      </c>
+      <c r="N28" s="9">
         <v>5.79</v>
       </c>
-      <c r="J27" s="7">
-        <v>79.7</v>
-      </c>
-      <c r="K27" s="7">
-        <v>284.8</v>
-      </c>
-      <c r="L27" s="13">
-        <v>1107.0999999999999</v>
-      </c>
-      <c r="M27" s="11">
-        <v>57.95</v>
-      </c>
-      <c r="N27" s="15">
-        <v>-9.06</v>
-      </c>
-      <c r="O27">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="5">
-        <v>247.82</v>
-      </c>
-      <c r="E28" s="6">
-        <v>20.9</v>
-      </c>
-      <c r="F28" s="5">
-        <v>92.64</v>
-      </c>
-      <c r="G28" s="5">
-        <v>59.32</v>
-      </c>
-      <c r="H28" s="5">
-        <v>42.96</v>
-      </c>
-      <c r="I28" s="5">
-        <v>23.97</v>
-      </c>
-      <c r="J28" s="7">
-        <v>56.2</v>
-      </c>
-      <c r="K28" s="7">
-        <v>38.1</v>
-      </c>
-      <c r="L28" s="8">
-        <v>2442.6</v>
-      </c>
-      <c r="M28" s="5">
-        <v>225.9</v>
-      </c>
-      <c r="N28" s="15">
-        <v>-8.75</v>
-      </c>
-      <c r="O28">
-        <v>20</v>
-      </c>
     </row>
     <row r="29" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="11">
-        <v>761.15</v>
-      </c>
-      <c r="E29" s="12">
-        <v>21.3</v>
-      </c>
-      <c r="F29" s="11">
-        <v>191.74</v>
-      </c>
-      <c r="G29" s="11">
-        <v>149.29</v>
-      </c>
-      <c r="H29" s="11">
-        <v>122.47</v>
-      </c>
-      <c r="I29" s="11">
-        <v>104.21</v>
+      <c r="A29" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="5">
+        <v>114.45</v>
+      </c>
+      <c r="E29" s="6">
+        <v>35.5</v>
+      </c>
+      <c r="F29" s="5">
+        <v>204.3</v>
+      </c>
+      <c r="G29" s="5">
+        <v>133.21</v>
+      </c>
+      <c r="H29" s="5">
+        <v>36.090000000000003</v>
+      </c>
+      <c r="I29" s="5">
+        <v>10.08</v>
       </c>
       <c r="J29" s="7">
-        <v>28.4</v>
+        <v>53.4</v>
       </c>
       <c r="K29" s="7">
-        <v>21.9</v>
-      </c>
-      <c r="L29" s="13">
-        <v>3104.3</v>
-      </c>
-      <c r="M29" s="11">
-        <v>675.16</v>
-      </c>
-      <c r="N29" s="15">
-        <v>-8.6300000000000008</v>
+        <v>269.10000000000002</v>
+      </c>
+      <c r="L29" s="8">
+        <v>2330</v>
+      </c>
+      <c r="M29" s="5">
+        <v>134.25</v>
+      </c>
+      <c r="N29" s="14">
+        <v>10.42</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D30" s="5">
-        <v>141.35</v>
+        <v>427.45</v>
       </c>
       <c r="E30" s="6">
-        <v>21.5</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="F30" s="5">
-        <v>45.36</v>
+        <v>149.21</v>
       </c>
       <c r="G30" s="5">
-        <v>37.799999999999997</v>
+        <v>136.38</v>
       </c>
       <c r="H30" s="5">
-        <v>31.18</v>
+        <v>130.69</v>
       </c>
       <c r="I30" s="5">
-        <v>16.579999999999998</v>
+        <v>107.26</v>
       </c>
       <c r="J30" s="7">
+        <v>9.4</v>
+      </c>
+      <c r="K30" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L30" s="8">
+        <v>2354.1999999999998</v>
+      </c>
+      <c r="M30" s="5">
+        <v>509.27</v>
+      </c>
+      <c r="N30" s="14">
+        <v>11.45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="5">
+        <v>247.82</v>
+      </c>
+      <c r="E31" s="6">
+        <v>20.9</v>
+      </c>
+      <c r="F31" s="5">
+        <v>92.64</v>
+      </c>
+      <c r="G31" s="5">
+        <v>59.32</v>
+      </c>
+      <c r="H31" s="5">
+        <v>42.96</v>
+      </c>
+      <c r="I31" s="5">
+        <v>23.97</v>
+      </c>
+      <c r="J31" s="7">
+        <v>56.2</v>
+      </c>
+      <c r="K31" s="7">
+        <v>38.1</v>
+      </c>
+      <c r="L31" s="8">
+        <v>2442.6</v>
+      </c>
+      <c r="M31" s="5">
+        <v>225.9</v>
+      </c>
+      <c r="N31" s="15">
+        <v>-8.75</v>
+      </c>
+      <c r="O31">
         <v>20</v>
-      </c>
-      <c r="K30" s="7">
-        <v>21.2</v>
-      </c>
-      <c r="L30" s="8">
-        <v>701.8</v>
-      </c>
-      <c r="M30" s="5">
-        <v>128.77000000000001</v>
-      </c>
-      <c r="N30" s="15">
-        <v>-8.3699999999999992</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="11">
-        <v>15.78</v>
-      </c>
-      <c r="E31" s="12">
-        <v>22.1</v>
-      </c>
-      <c r="F31" s="11">
-        <v>45.22</v>
-      </c>
-      <c r="G31" s="11">
-        <v>23.1</v>
-      </c>
-      <c r="H31" s="11">
-        <v>20.21</v>
-      </c>
-      <c r="I31" s="11">
-        <v>12.7</v>
-      </c>
-      <c r="J31" s="7">
-        <v>95.8</v>
-      </c>
-      <c r="K31" s="7">
-        <v>14.3</v>
-      </c>
-      <c r="L31" s="13">
-        <v>516.70000000000005</v>
-      </c>
-      <c r="M31" s="11">
-        <v>14.92</v>
-      </c>
-      <c r="N31" s="15">
-        <v>-8.3699999999999992</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="11">
+        <v>577.4</v>
+      </c>
+      <c r="E32" s="12">
+        <v>16.3</v>
+      </c>
+      <c r="F32" s="11">
+        <v>77.510000000000005</v>
+      </c>
+      <c r="G32" s="11">
+        <v>66.75</v>
+      </c>
+      <c r="H32" s="11">
+        <v>48.81</v>
+      </c>
+      <c r="I32" s="11">
+        <v>48.17</v>
+      </c>
+      <c r="J32" s="7">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="K32" s="7">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="L32" s="13">
+        <v>2637.3</v>
+      </c>
+      <c r="M32" s="11">
+        <v>577.5</v>
+      </c>
+      <c r="N32" s="15">
+        <v>-14.75</v>
+      </c>
+      <c r="O32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="5">
+        <v>1685.6</v>
+      </c>
+      <c r="E33" s="6">
+        <v>29.9</v>
+      </c>
+      <c r="F33" s="5">
+        <v>134.52000000000001</v>
+      </c>
+      <c r="G33" s="5">
+        <v>107.83</v>
+      </c>
+      <c r="H33" s="5">
+        <v>86.26</v>
+      </c>
+      <c r="I33" s="5">
+        <v>81.459999999999994</v>
+      </c>
+      <c r="J33" s="7">
+        <v>24.8</v>
+      </c>
+      <c r="K33" s="7">
+        <v>25</v>
+      </c>
+      <c r="L33" s="8">
+        <v>2806.8</v>
+      </c>
+      <c r="M33" s="5">
+        <v>1839.65</v>
+      </c>
+      <c r="N33" s="9">
+        <v>4.25</v>
+      </c>
+      <c r="O33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="5">
-        <v>183.07</v>
-      </c>
-      <c r="E32" s="6">
-        <v>22.4</v>
-      </c>
-      <c r="F32" s="5">
-        <v>468.72</v>
-      </c>
-      <c r="G32" s="5">
-        <v>387.94</v>
-      </c>
-      <c r="H32" s="5">
-        <v>310.44</v>
-      </c>
-      <c r="I32" s="5">
-        <v>219.04</v>
-      </c>
-      <c r="J32" s="7">
-        <v>20.8</v>
-      </c>
-      <c r="K32" s="7">
-        <v>25</v>
-      </c>
-      <c r="L32" s="8">
-        <v>8908.1</v>
-      </c>
-      <c r="M32" s="5">
-        <v>187.49</v>
-      </c>
-      <c r="N32" s="15">
-        <v>-7.57</v>
-      </c>
-      <c r="O32">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" s="11">
-        <v>43.88</v>
-      </c>
-      <c r="E33" s="12">
-        <v>22.6</v>
-      </c>
-      <c r="F33" s="11">
-        <v>924.77</v>
-      </c>
-      <c r="G33" s="11">
-        <v>539.12</v>
-      </c>
-      <c r="H33" s="11">
-        <v>228.27</v>
-      </c>
-      <c r="I33" s="11">
-        <v>143.57</v>
-      </c>
-      <c r="J33" s="7">
-        <v>71.5</v>
-      </c>
-      <c r="K33" s="7">
-        <v>136.19999999999999</v>
-      </c>
-      <c r="L33" s="13">
-        <v>20209.3</v>
-      </c>
-      <c r="M33" s="11">
-        <v>43.66</v>
-      </c>
-      <c r="N33" s="15">
-        <v>-6.71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="5">
-        <v>325.7</v>
-      </c>
-      <c r="E34" s="6">
-        <v>22.7</v>
-      </c>
-      <c r="F34" s="5">
-        <v>160.94</v>
-      </c>
-      <c r="G34" s="5">
-        <v>144.62</v>
-      </c>
-      <c r="H34" s="5">
-        <v>73.62</v>
-      </c>
-      <c r="I34" s="5">
-        <v>59.93</v>
+      <c r="D34" s="11">
+        <v>525.65</v>
+      </c>
+      <c r="E34" s="12">
+        <v>27.4</v>
+      </c>
+      <c r="F34" s="11">
+        <v>130.56</v>
+      </c>
+      <c r="G34" s="11">
+        <v>88.12</v>
+      </c>
+      <c r="H34" s="11">
+        <v>62.54</v>
+      </c>
+      <c r="I34" s="11">
+        <v>48.44</v>
       </c>
       <c r="J34" s="7">
-        <v>11.3</v>
+        <v>48.2</v>
       </c>
       <c r="K34" s="7">
-        <v>96.4</v>
-      </c>
-      <c r="L34" s="8">
-        <v>5083.3999999999996</v>
-      </c>
-      <c r="M34" s="5">
-        <v>312.41000000000003</v>
-      </c>
-      <c r="N34" s="15">
-        <v>-6.61</v>
+        <v>40.9</v>
+      </c>
+      <c r="L34" s="13">
+        <v>2938.1</v>
+      </c>
+      <c r="M34" s="11">
+        <v>522.92999999999995</v>
+      </c>
+      <c r="N34" s="9">
+        <v>0.87</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>101</v>
+        <v>196</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D35" s="11">
-        <v>447.25</v>
+        <v>264.8</v>
       </c>
       <c r="E35" s="12">
-        <v>23.7</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="F35" s="11">
-        <v>131.87</v>
+        <v>376.28</v>
       </c>
       <c r="G35" s="11">
-        <v>58.05</v>
+        <v>280.61</v>
       </c>
       <c r="H35" s="11">
-        <v>31.87</v>
+        <v>97.67</v>
       </c>
       <c r="I35" s="11">
-        <v>75.05</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="J35" s="7">
-        <v>127.1</v>
+        <v>34.1</v>
       </c>
       <c r="K35" s="7">
-        <v>82.1</v>
+        <v>187.3</v>
       </c>
       <c r="L35" s="13">
-        <v>3321.9</v>
+        <v>3016</v>
       </c>
       <c r="M35" s="11">
-        <v>502.39</v>
-      </c>
-      <c r="N35" s="15">
-        <v>-6.11</v>
+        <v>393.9</v>
+      </c>
+      <c r="N35" s="14">
+        <v>12.74</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="5">
-        <v>950.25</v>
-      </c>
-      <c r="E36" s="6">
-        <v>24.1</v>
-      </c>
-      <c r="F36" s="5">
-        <v>52.85</v>
-      </c>
-      <c r="G36" s="5">
-        <v>48.36</v>
-      </c>
-      <c r="H36" s="5">
-        <v>40.29</v>
-      </c>
-      <c r="I36" s="5">
-        <v>21.8</v>
+      <c r="A36" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="11">
+        <v>761.15</v>
+      </c>
+      <c r="E36" s="12">
+        <v>21.3</v>
+      </c>
+      <c r="F36" s="11">
+        <v>191.74</v>
+      </c>
+      <c r="G36" s="11">
+        <v>149.29</v>
+      </c>
+      <c r="H36" s="11">
+        <v>122.47</v>
+      </c>
+      <c r="I36" s="11">
+        <v>104.21</v>
       </c>
       <c r="J36" s="7">
-        <v>9.3000000000000007</v>
+        <v>28.4</v>
       </c>
       <c r="K36" s="7">
-        <v>20</v>
-      </c>
-      <c r="L36" s="8">
-        <v>1694.6</v>
-      </c>
-      <c r="M36" s="5">
-        <v>916.54</v>
+        <v>21.9</v>
+      </c>
+      <c r="L36" s="13">
+        <v>3104.3</v>
+      </c>
+      <c r="M36" s="11">
+        <v>675.16</v>
       </c>
       <c r="N36" s="15">
-        <v>-6.02</v>
+        <v>-8.6300000000000008</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="11">
-        <v>928.55</v>
-      </c>
-      <c r="E37" s="12">
-        <v>24.3</v>
-      </c>
-      <c r="F37" s="11">
-        <v>345.41</v>
-      </c>
-      <c r="G37" s="11">
-        <v>314.92</v>
-      </c>
-      <c r="H37" s="11">
-        <v>299.58999999999997</v>
-      </c>
-      <c r="I37" s="11">
-        <v>208.33</v>
+      <c r="A37" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="5">
+        <v>616.04999999999995</v>
+      </c>
+      <c r="E37" s="6">
+        <v>38.5</v>
+      </c>
+      <c r="F37" s="5">
+        <v>212.51</v>
+      </c>
+      <c r="G37" s="5">
+        <v>189.35</v>
+      </c>
+      <c r="H37" s="5">
+        <v>140.97</v>
+      </c>
+      <c r="I37" s="5">
+        <v>97.33</v>
       </c>
       <c r="J37" s="7">
-        <v>9.6999999999999993</v>
+        <v>12.2</v>
       </c>
       <c r="K37" s="7">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="L37" s="13">
-        <v>5358.1</v>
-      </c>
-      <c r="M37" s="11">
-        <v>889.38</v>
-      </c>
-      <c r="N37" s="15">
-        <v>-4.59</v>
+        <v>34.299999999999997</v>
+      </c>
+      <c r="L37" s="8">
+        <v>3206.2</v>
+      </c>
+      <c r="M37" s="5">
+        <v>830.14</v>
+      </c>
+      <c r="N37" s="14">
+        <v>16.27</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="18" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D38" s="5">
-        <v>1922.4</v>
+        <v>185.54</v>
       </c>
       <c r="E38" s="6">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
       <c r="F38" s="5">
-        <v>924.36</v>
+        <v>182.95</v>
       </c>
       <c r="G38" s="5">
-        <v>681.33</v>
+        <v>176.3</v>
       </c>
       <c r="H38" s="5">
-        <v>498.18</v>
+        <v>108.43</v>
       </c>
       <c r="I38" s="5">
-        <v>532.02</v>
+        <v>54.98</v>
       </c>
       <c r="J38" s="7">
-        <v>35.700000000000003</v>
+        <v>3.8</v>
       </c>
       <c r="K38" s="7">
-        <v>36.799999999999997</v>
+        <v>62.6</v>
       </c>
       <c r="L38" s="8">
-        <v>36690</v>
+        <v>3229.8</v>
       </c>
       <c r="M38" s="5">
-        <v>1738.52</v>
+        <v>204.13</v>
       </c>
       <c r="N38" s="15">
-        <v>-4.42</v>
+        <v>-2.36</v>
+      </c>
+      <c r="O38">
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="18" t="s">
-        <v>108</v>
+      <c r="A39" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="D39" s="11">
-        <v>402.5</v>
+        <v>447.25</v>
       </c>
       <c r="E39" s="12">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
       <c r="F39" s="11">
-        <v>357.3</v>
+        <v>131.87</v>
       </c>
       <c r="G39" s="11">
-        <v>217.33</v>
+        <v>58.05</v>
       </c>
       <c r="H39" s="11">
-        <v>100.42</v>
+        <v>31.87</v>
       </c>
       <c r="I39" s="11">
-        <v>4.75</v>
+        <v>75.05</v>
       </c>
       <c r="J39" s="7">
-        <v>64.400000000000006</v>
+        <v>127.1</v>
       </c>
       <c r="K39" s="7">
-        <v>116.4</v>
+        <v>82.1</v>
       </c>
       <c r="L39" s="13">
-        <v>5168.1000000000004</v>
+        <v>3321.9</v>
       </c>
       <c r="M39" s="11">
-        <v>431.46</v>
+        <v>502.39</v>
       </c>
       <c r="N39" s="15">
-        <v>-4.0599999999999996</v>
-      </c>
-      <c r="O39">
-        <v>12</v>
+        <v>-6.11</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="18" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D40" s="5">
-        <v>608.9</v>
+        <v>558.1</v>
       </c>
       <c r="E40" s="6">
-        <v>24.9</v>
+        <v>29.6</v>
       </c>
       <c r="F40" s="5">
-        <v>557.02</v>
+        <v>198.66</v>
       </c>
       <c r="G40" s="5">
-        <v>425.82</v>
+        <v>141.63999999999999</v>
       </c>
       <c r="H40" s="5">
-        <v>265.93</v>
+        <v>109.78</v>
       </c>
       <c r="I40" s="5">
-        <v>151.12</v>
+        <v>72.97</v>
       </c>
       <c r="J40" s="7">
-        <v>30.8</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="K40" s="7">
-        <v>60.1</v>
+        <v>29</v>
       </c>
       <c r="L40" s="8">
-        <v>20764.900000000001</v>
+        <v>3402.9</v>
       </c>
       <c r="M40" s="5">
-        <v>578.76</v>
-      </c>
-      <c r="N40" s="15">
-        <v>-3.64</v>
-      </c>
-      <c r="O40">
-        <v>8</v>
+        <v>581.69000000000005</v>
+      </c>
+      <c r="N40" s="9">
+        <v>3.7</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="19" t="s">
-        <v>112</v>
+      <c r="A41" s="18" t="s">
+        <v>173</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="D41" s="11">
-        <v>95.83</v>
+        <v>166.28</v>
       </c>
       <c r="E41" s="12">
-        <v>25.8</v>
+        <v>33.9</v>
       </c>
       <c r="F41" s="11">
-        <v>57.65</v>
+        <v>297.57</v>
       </c>
       <c r="G41" s="11">
-        <v>40.56</v>
+        <v>267.61</v>
       </c>
       <c r="H41" s="11">
-        <v>25.69</v>
+        <v>219.44</v>
       </c>
       <c r="I41" s="11">
-        <v>21.5</v>
+        <v>14.29</v>
       </c>
       <c r="J41" s="7">
-        <v>42.2</v>
+        <v>11.2</v>
       </c>
       <c r="K41" s="7">
-        <v>57.9</v>
+        <v>22</v>
       </c>
       <c r="L41" s="13">
-        <v>1924.9</v>
+        <v>3604.7</v>
       </c>
       <c r="M41" s="11">
-        <v>80.349999999999994</v>
-      </c>
-      <c r="N41" s="15">
-        <v>-3.39</v>
+        <v>184.16</v>
+      </c>
+      <c r="N41" s="9">
+        <v>9</v>
+      </c>
+      <c r="O41">
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D42" s="5">
-        <v>185.54</v>
-      </c>
-      <c r="E42" s="6">
-        <v>26.1</v>
-      </c>
-      <c r="F42" s="5">
-        <v>182.95</v>
-      </c>
-      <c r="G42" s="5">
-        <v>176.3</v>
-      </c>
-      <c r="H42" s="5">
-        <v>108.43</v>
-      </c>
-      <c r="I42" s="5">
-        <v>54.98</v>
-      </c>
+      <c r="D42" s="11">
+        <v>278.8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>29.8</v>
+      </c>
+      <c r="F42" s="11">
+        <v>151.59</v>
+      </c>
+      <c r="G42" s="11">
+        <v>103.56</v>
+      </c>
+      <c r="H42" s="11">
+        <v>39.92</v>
+      </c>
+      <c r="I42" s="11"/>
       <c r="J42" s="7">
-        <v>3.8</v>
+        <v>46.4</v>
       </c>
       <c r="K42" s="7">
-        <v>62.6</v>
-      </c>
-      <c r="L42" s="8">
-        <v>3229.8</v>
-      </c>
-      <c r="M42" s="5">
-        <v>204.13</v>
-      </c>
-      <c r="N42" s="15">
-        <v>-2.36</v>
-      </c>
-      <c r="O42">
-        <v>50</v>
+        <v>159.4</v>
+      </c>
+      <c r="L42" s="13">
+        <v>3663.6</v>
+      </c>
+      <c r="M42" s="11">
+        <v>276.02999999999997</v>
+      </c>
+      <c r="N42" s="9">
+        <v>3.77</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D43" s="11">
-        <v>878.85</v>
-      </c>
-      <c r="E43" s="12">
-        <v>26.3</v>
-      </c>
-      <c r="F43" s="11">
-        <v>123.98</v>
-      </c>
-      <c r="G43" s="11">
-        <v>103.24</v>
-      </c>
-      <c r="H43" s="11">
-        <v>90.44</v>
-      </c>
-      <c r="I43" s="11">
-        <v>133.88999999999999</v>
+      <c r="A43" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D43" s="5">
+        <v>265.14999999999998</v>
+      </c>
+      <c r="E43" s="6">
+        <v>34.9</v>
+      </c>
+      <c r="F43" s="5">
+        <v>242.01</v>
+      </c>
+      <c r="G43" s="5">
+        <v>180.09</v>
+      </c>
+      <c r="H43" s="5">
+        <v>93.87</v>
+      </c>
+      <c r="I43" s="5">
+        <v>116.06</v>
       </c>
       <c r="J43" s="7">
-        <v>20.100000000000001</v>
+        <v>34.4</v>
       </c>
       <c r="K43" s="7">
-        <v>14.2</v>
-      </c>
-      <c r="L43" s="13">
-        <v>1320.7</v>
-      </c>
-      <c r="M43" s="11">
-        <v>805.44</v>
-      </c>
-      <c r="N43" s="15">
-        <v>-1.53</v>
+        <v>91.9</v>
+      </c>
+      <c r="L43" s="8">
+        <v>3716.1</v>
+      </c>
+      <c r="M43" s="5">
+        <v>291.56</v>
+      </c>
+      <c r="N43" s="9">
+        <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D44" s="5">
-        <v>2426</v>
-      </c>
-      <c r="E44" s="6">
-        <v>26.4</v>
-      </c>
-      <c r="F44" s="5">
-        <v>363.99</v>
-      </c>
-      <c r="G44" s="5">
-        <v>326.48</v>
-      </c>
-      <c r="H44" s="5">
-        <v>248.07</v>
-      </c>
-      <c r="I44" s="5">
-        <v>209.11</v>
+      <c r="A44" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="11">
+        <v>662.15</v>
+      </c>
+      <c r="E44" s="12">
+        <v>16</v>
+      </c>
+      <c r="F44" s="11">
+        <v>127.66</v>
+      </c>
+      <c r="G44" s="11">
+        <v>80.989999999999995</v>
+      </c>
+      <c r="H44" s="11">
+        <v>78.58</v>
+      </c>
+      <c r="I44" s="11">
+        <v>18.41</v>
       </c>
       <c r="J44" s="7">
-        <v>11.5</v>
+        <v>57.6</v>
       </c>
       <c r="K44" s="7">
-        <v>31.6</v>
-      </c>
-      <c r="L44" s="8">
-        <v>7821.9</v>
-      </c>
-      <c r="M44" s="5">
-        <v>2463.81</v>
+        <v>3.1</v>
+      </c>
+      <c r="L44" s="13">
+        <v>4163.8999999999996</v>
+      </c>
+      <c r="M44" s="11">
+        <v>563.22</v>
       </c>
       <c r="N44" s="15">
-        <v>-1.01</v>
+        <v>-16.29</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="10" t="s">
-        <v>120</v>
+      <c r="A45" s="18" t="s">
+        <v>35</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D45" s="11">
-        <v>3573.4</v>
+        <v>695.55</v>
       </c>
       <c r="E45" s="12">
-        <v>26.7</v>
+        <v>14.6</v>
       </c>
       <c r="F45" s="11">
-        <v>1056</v>
+        <v>142.27000000000001</v>
       </c>
       <c r="G45" s="11">
-        <v>920.39</v>
+        <v>126.64</v>
       </c>
       <c r="H45" s="11">
-        <v>816.17</v>
+        <v>101.1</v>
       </c>
       <c r="I45" s="11">
-        <v>587.98</v>
+        <v>136.56</v>
       </c>
       <c r="J45" s="7">
-        <v>14.7</v>
+        <v>12.3</v>
       </c>
       <c r="K45" s="7">
-        <v>12.8</v>
+        <v>25.3</v>
       </c>
       <c r="L45" s="13">
-        <v>44810.3</v>
+        <v>4429.3</v>
       </c>
       <c r="M45" s="11">
-        <v>3150.23</v>
+        <v>596.47</v>
       </c>
       <c r="N45" s="15">
-        <v>-0.02</v>
+        <v>-25.79</v>
+      </c>
+      <c r="O45">
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C46" s="4" t="s">
+      <c r="A46" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D46" s="5">
-        <v>5075</v>
-      </c>
-      <c r="E46" s="6">
-        <v>26.7</v>
-      </c>
-      <c r="F46" s="5">
-        <v>5741.73</v>
-      </c>
-      <c r="G46" s="5">
-        <v>4378.4799999999996</v>
-      </c>
-      <c r="H46" s="5">
-        <v>3744.83</v>
-      </c>
-      <c r="I46" s="5">
-        <v>2809.96</v>
+      <c r="D46" s="11">
+        <v>317.5</v>
+      </c>
+      <c r="E46" s="12">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="F46" s="11">
+        <v>170.6</v>
+      </c>
+      <c r="G46" s="11">
+        <v>117.03</v>
+      </c>
+      <c r="H46" s="11">
+        <v>90.81</v>
+      </c>
+      <c r="I46" s="11">
+        <v>84.42</v>
       </c>
       <c r="J46" s="7">
-        <v>31.1</v>
+        <v>45.8</v>
       </c>
       <c r="K46" s="7">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="L46" s="8">
-        <v>103433</v>
-      </c>
-      <c r="M46" s="5">
-        <v>5266.85</v>
-      </c>
-      <c r="N46" s="9">
-        <v>0.31</v>
+        <v>28.9</v>
+      </c>
+      <c r="L46" s="13">
+        <v>4689.1000000000004</v>
+      </c>
+      <c r="M46" s="11">
+        <v>314.75</v>
+      </c>
+      <c r="N46" s="14">
+        <v>13.06</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D47" s="11">
-        <v>2516</v>
+        <v>491.3</v>
       </c>
       <c r="E47" s="12">
-        <v>26.8</v>
+        <v>17.3</v>
       </c>
       <c r="F47" s="11">
-        <v>951.71</v>
+        <v>182.58</v>
       </c>
       <c r="G47" s="11">
-        <v>836.35</v>
+        <v>165.63</v>
       </c>
       <c r="H47" s="11">
-        <v>680.49</v>
+        <v>132.27000000000001</v>
       </c>
       <c r="I47" s="11">
-        <v>479.57</v>
+        <v>87.8</v>
       </c>
       <c r="J47" s="7">
-        <v>13.8</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="K47" s="7">
-        <v>22.9</v>
+        <v>25.2</v>
       </c>
       <c r="L47" s="13">
-        <v>36521.699999999997</v>
+        <v>4985.8</v>
       </c>
       <c r="M47" s="11">
-        <v>2677.23</v>
-      </c>
-      <c r="N47" s="9">
-        <v>0.51</v>
+        <v>452.97</v>
+      </c>
+      <c r="N47" s="15">
+        <v>-13.56</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="19" t="s">
-        <v>126</v>
+      <c r="A48" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D48" s="5">
-        <v>4405</v>
+        <v>325.7</v>
       </c>
       <c r="E48" s="6">
-        <v>27</v>
+        <v>22.7</v>
       </c>
       <c r="F48" s="5">
-        <v>552.5</v>
+        <v>160.94</v>
       </c>
       <c r="G48" s="5">
-        <v>506.68</v>
+        <v>144.62</v>
       </c>
       <c r="H48" s="5">
-        <v>442.56</v>
+        <v>73.62</v>
       </c>
       <c r="I48" s="5">
-        <v>293.45999999999998</v>
+        <v>59.93</v>
       </c>
       <c r="J48" s="7">
-        <v>9</v>
+        <v>11.3</v>
       </c>
       <c r="K48" s="7">
-        <v>14.5</v>
+        <v>96.4</v>
       </c>
       <c r="L48" s="8">
-        <v>20711.900000000001</v>
+        <v>5083.3999999999996</v>
       </c>
       <c r="M48" s="5">
-        <v>3812.6</v>
-      </c>
-      <c r="N48" s="9">
-        <v>0.52</v>
+        <v>312.41000000000003</v>
+      </c>
+      <c r="N48" s="15">
+        <v>-6.61</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="18" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C49" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49" s="11">
+        <v>402.5</v>
+      </c>
+      <c r="E49" s="12">
+        <v>24.6</v>
+      </c>
+      <c r="F49" s="11">
+        <v>357.3</v>
+      </c>
+      <c r="G49" s="11">
+        <v>217.33</v>
+      </c>
+      <c r="H49" s="11">
+        <v>100.42</v>
+      </c>
+      <c r="I49" s="11">
+        <v>4.75</v>
+      </c>
+      <c r="J49" s="7">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="K49" s="7">
+        <v>116.4</v>
+      </c>
+      <c r="L49" s="13">
+        <v>5168.1000000000004</v>
+      </c>
+      <c r="M49" s="11">
+        <v>431.46</v>
+      </c>
+      <c r="N49" s="15">
+        <v>-4.0599999999999996</v>
+      </c>
+      <c r="O49">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D49" s="11">
-        <v>677.65</v>
-      </c>
-      <c r="E49" s="12">
-        <v>27.2</v>
-      </c>
-      <c r="F49" s="11">
-        <v>250.8</v>
-      </c>
-      <c r="G49" s="11">
-        <v>167.03</v>
-      </c>
-      <c r="H49" s="11">
-        <v>140.61000000000001</v>
-      </c>
-      <c r="I49" s="11">
-        <v>124.69</v>
-      </c>
-      <c r="J49" s="7">
-        <v>50.2</v>
-      </c>
-      <c r="K49" s="7">
-        <v>18.8</v>
-      </c>
-      <c r="L49" s="13">
-        <v>9018</v>
-      </c>
-      <c r="M49" s="11">
-        <v>648.29999999999995</v>
-      </c>
-      <c r="N49" s="9">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" s="5">
-        <v>283.64999999999998</v>
-      </c>
-      <c r="E50" s="6">
-        <v>27.3</v>
-      </c>
-      <c r="F50" s="5">
-        <v>264.39</v>
-      </c>
-      <c r="G50" s="5">
-        <v>214.27</v>
-      </c>
-      <c r="H50" s="5">
-        <v>44.5</v>
-      </c>
-      <c r="I50" s="5">
-        <v>40.74</v>
+      <c r="D50" s="11">
+        <v>786.4</v>
+      </c>
+      <c r="E50" s="12">
+        <v>15</v>
+      </c>
+      <c r="F50" s="11">
+        <v>351.66</v>
+      </c>
+      <c r="G50" s="11">
+        <v>322.41000000000003</v>
+      </c>
+      <c r="H50" s="11">
+        <v>251.33</v>
+      </c>
+      <c r="I50" s="11">
+        <v>248.79</v>
       </c>
       <c r="J50" s="7">
-        <v>23.4</v>
+        <v>9.1</v>
       </c>
       <c r="K50" s="7">
-        <v>381.5</v>
-      </c>
-      <c r="L50" s="8">
-        <v>8524.7000000000007</v>
-      </c>
-      <c r="M50" s="5">
-        <v>318.61</v>
-      </c>
-      <c r="N50" s="9">
-        <v>0.7</v>
+        <v>28.3</v>
+      </c>
+      <c r="L50" s="13">
+        <v>5175.8</v>
+      </c>
+      <c r="M50" s="11">
+        <v>701.31</v>
+      </c>
+      <c r="N50" s="15">
+        <v>-18.920000000000002</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="19" t="s">
-        <v>132</v>
+      <c r="A51" s="10" t="s">
+        <v>104</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D51" s="11">
-        <v>525.65</v>
+        <v>928.55</v>
       </c>
       <c r="E51" s="12">
-        <v>27.4</v>
+        <v>24.3</v>
       </c>
       <c r="F51" s="11">
-        <v>130.56</v>
+        <v>345.41</v>
       </c>
       <c r="G51" s="11">
-        <v>88.12</v>
+        <v>314.92</v>
       </c>
       <c r="H51" s="11">
-        <v>62.54</v>
+        <v>299.58999999999997</v>
       </c>
       <c r="I51" s="11">
-        <v>48.44</v>
+        <v>208.33</v>
       </c>
       <c r="J51" s="7">
-        <v>48.2</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="K51" s="7">
-        <v>40.9</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="L51" s="13">
-        <v>2938.1</v>
+        <v>5358.1</v>
       </c>
       <c r="M51" s="11">
-        <v>522.92999999999995</v>
-      </c>
-      <c r="N51" s="9">
-        <v>0.87</v>
+        <v>889.38</v>
+      </c>
+      <c r="N51" s="15">
+        <v>-4.59</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="18" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D52" s="5">
-        <v>996.2</v>
+        <v>526.95000000000005</v>
       </c>
       <c r="E52" s="6">
-        <v>27.8</v>
+        <v>20.8</v>
       </c>
       <c r="F52" s="5">
-        <v>448.7</v>
+        <v>258.89</v>
       </c>
       <c r="G52" s="5">
-        <v>378.12</v>
+        <v>203.86</v>
       </c>
       <c r="H52" s="5">
-        <v>271.02999999999997</v>
+        <v>93.49</v>
       </c>
       <c r="I52" s="5">
-        <v>96.61</v>
+        <v>38.909999999999997</v>
       </c>
       <c r="J52" s="7">
-        <v>18.7</v>
+        <v>27</v>
       </c>
       <c r="K52" s="7">
-        <v>39.5</v>
+        <v>118</v>
       </c>
       <c r="L52" s="8">
-        <v>11641.6</v>
+        <v>5936.1</v>
       </c>
       <c r="M52" s="5">
-        <v>1077.79</v>
-      </c>
-      <c r="N52" s="9">
-        <v>1</v>
+        <v>511.86</v>
+      </c>
+      <c r="N52" s="15">
+        <v>-9.11</v>
       </c>
       <c r="O52">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D53" s="11">
-        <v>280.8</v>
-      </c>
-      <c r="E53" s="12">
-        <v>28.2</v>
-      </c>
-      <c r="F53" s="11">
-        <v>19.3</v>
-      </c>
-      <c r="G53" s="11">
-        <v>12.8</v>
-      </c>
-      <c r="H53" s="11">
-        <v>10.02</v>
-      </c>
-      <c r="I53" s="11">
-        <v>2.88</v>
+      <c r="A53" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D53" s="5">
+        <v>210.95</v>
+      </c>
+      <c r="E53" s="6">
+        <v>16.3</v>
+      </c>
+      <c r="F53" s="5">
+        <v>369.38</v>
+      </c>
+      <c r="G53" s="5">
+        <v>245.58</v>
+      </c>
+      <c r="H53" s="5">
+        <v>135.76</v>
+      </c>
+      <c r="I53" s="5">
+        <v>132.41</v>
       </c>
       <c r="J53" s="7">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
       <c r="K53" s="7">
-        <v>27.7</v>
-      </c>
-      <c r="L53" s="13">
-        <v>448.6</v>
-      </c>
-      <c r="M53" s="11">
-        <v>293.79000000000002</v>
-      </c>
-      <c r="N53" s="9">
-        <v>1.69</v>
+        <v>80.900000000000006</v>
+      </c>
+      <c r="L53" s="8">
+        <v>6226.3</v>
+      </c>
+      <c r="M53" s="5">
+        <v>213.11</v>
+      </c>
+      <c r="N53" s="15">
+        <v>-14.46</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
-        <v>138</v>
+      <c r="A54" s="18" t="s">
+        <v>163</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D54" s="5">
-        <v>566.6</v>
+        <v>482.4</v>
       </c>
       <c r="E54" s="6">
-        <v>28.7</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="F54" s="5">
-        <v>100.84</v>
+        <v>403.59</v>
       </c>
       <c r="G54" s="5">
-        <v>66.47</v>
+        <v>328.68</v>
       </c>
       <c r="H54" s="5">
-        <v>42.75</v>
+        <v>233.2</v>
       </c>
       <c r="I54" s="5">
-        <v>90.32</v>
+        <v>107.57</v>
       </c>
       <c r="J54" s="7">
-        <v>51.7</v>
+        <v>22.8</v>
       </c>
       <c r="K54" s="7">
-        <v>55.5</v>
+        <v>40.9</v>
       </c>
       <c r="L54" s="8">
-        <v>1170.0999999999999</v>
+        <v>6312.7</v>
       </c>
       <c r="M54" s="5">
-        <v>508.39</v>
+        <v>513.78</v>
       </c>
       <c r="N54" s="9">
-        <v>2.46</v>
+        <v>5.64</v>
+      </c>
+      <c r="O54">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>141</v>
+        <v>216</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D55" s="11">
-        <v>160</v>
+        <v>741.75</v>
       </c>
       <c r="E55" s="12">
-        <v>28.8</v>
+        <v>39.4</v>
       </c>
       <c r="F55" s="11">
-        <v>3859.7</v>
+        <v>680.86</v>
       </c>
       <c r="G55" s="11">
-        <v>3803</v>
+        <v>304.38</v>
       </c>
       <c r="H55" s="11">
-        <v>2716.2</v>
+        <v>31.88</v>
       </c>
       <c r="I55" s="11">
-        <v>1495.6</v>
+        <v>341.96</v>
       </c>
       <c r="J55" s="7">
-        <v>1.5</v>
+        <v>123.7</v>
       </c>
       <c r="K55" s="7">
-        <v>40</v>
+        <v>854.7</v>
       </c>
       <c r="L55" s="13">
-        <v>165371.9</v>
+        <v>6432.7</v>
       </c>
       <c r="M55" s="11">
-        <v>141.05000000000001</v>
-      </c>
-      <c r="N55" s="9">
-        <v>2.95</v>
+        <v>864.35</v>
+      </c>
+      <c r="N55" s="14">
+        <v>17.559999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
-        <v>142</v>
+      <c r="A56" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D56" s="5">
-        <v>710.85</v>
+        <v>551.5</v>
       </c>
       <c r="E56" s="6">
-        <v>28.8</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="F56" s="5">
-        <v>256.13</v>
+        <v>213.13</v>
       </c>
       <c r="G56" s="5">
-        <v>211.19</v>
+        <v>149.35</v>
       </c>
       <c r="H56" s="5">
-        <v>133.29</v>
+        <v>81.67</v>
       </c>
       <c r="I56" s="5">
-        <v>108.58</v>
+        <v>35.57</v>
       </c>
       <c r="J56" s="7">
-        <v>21.3</v>
+        <v>42.7</v>
       </c>
       <c r="K56" s="7">
-        <v>58.4</v>
+        <v>82.9</v>
       </c>
       <c r="L56" s="8">
-        <v>8939.9</v>
+        <v>6644.3</v>
       </c>
       <c r="M56" s="5">
-        <v>708.65</v>
-      </c>
-      <c r="N56" s="9">
-        <v>3.19</v>
+        <v>505.97</v>
+      </c>
+      <c r="N56" s="15">
+        <v>-9.7100000000000009</v>
+      </c>
+      <c r="O56">
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D57" s="11">
-        <v>653.1</v>
-      </c>
-      <c r="E57" s="12">
-        <v>28.9</v>
-      </c>
-      <c r="F57" s="11">
-        <v>216.75</v>
-      </c>
-      <c r="G57" s="11">
-        <v>166.56</v>
-      </c>
-      <c r="H57" s="11">
-        <v>127.17</v>
-      </c>
-      <c r="I57" s="11">
-        <v>76.52</v>
+      <c r="A57" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="5">
+        <v>1037.0999999999999</v>
+      </c>
+      <c r="E57" s="6">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="F57" s="5">
+        <v>412.74</v>
+      </c>
+      <c r="G57" s="5">
+        <v>375.21</v>
+      </c>
+      <c r="H57" s="5">
+        <v>362.78</v>
+      </c>
+      <c r="I57" s="5">
+        <v>290.64</v>
       </c>
       <c r="J57" s="7">
-        <v>30.1</v>
+        <v>10</v>
       </c>
       <c r="K57" s="7">
-        <v>31</v>
-      </c>
-      <c r="L57" s="13">
-        <v>8224.7000000000007</v>
-      </c>
-      <c r="M57" s="11">
-        <v>622.9</v>
+        <v>3.4</v>
+      </c>
+      <c r="L57" s="8">
+        <v>7222.1</v>
+      </c>
+      <c r="M57" s="5">
+        <v>1131.8399999999999</v>
       </c>
       <c r="N57" s="9">
-        <v>3.68</v>
+        <v>8.4600000000000009</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" s="5">
-        <v>558.1</v>
-      </c>
-      <c r="E58" s="6">
-        <v>29.6</v>
-      </c>
-      <c r="F58" s="5">
-        <v>198.66</v>
-      </c>
-      <c r="G58" s="5">
-        <v>141.63999999999999</v>
-      </c>
-      <c r="H58" s="5">
-        <v>109.78</v>
-      </c>
-      <c r="I58" s="5">
-        <v>72.97</v>
+        <v>71</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D58" s="11">
+        <v>915.35</v>
+      </c>
+      <c r="E58" s="12">
+        <v>19.8</v>
+      </c>
+      <c r="F58" s="11">
+        <v>209.12</v>
+      </c>
+      <c r="G58" s="11">
+        <v>187.96</v>
+      </c>
+      <c r="H58" s="11">
+        <v>119.11</v>
+      </c>
+      <c r="I58" s="11">
+        <v>89.86</v>
       </c>
       <c r="J58" s="7">
-        <v>40.299999999999997</v>
+        <v>11.3</v>
       </c>
       <c r="K58" s="7">
-        <v>29</v>
-      </c>
-      <c r="L58" s="8">
-        <v>3402.9</v>
-      </c>
-      <c r="M58" s="5">
-        <v>581.69000000000005</v>
-      </c>
-      <c r="N58" s="9">
-        <v>3.7</v>
+        <v>57.8</v>
+      </c>
+      <c r="L58" s="13">
+        <v>7444.7</v>
+      </c>
+      <c r="M58" s="11">
+        <v>812.41</v>
+      </c>
+      <c r="N58" s="15">
+        <v>-10.44</v>
+      </c>
+      <c r="O58">
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C59" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D59" s="11">
-        <v>278.8</v>
-      </c>
-      <c r="E59" s="12">
-        <v>29.8</v>
-      </c>
-      <c r="F59" s="11">
-        <v>151.59</v>
-      </c>
-      <c r="G59" s="11">
-        <v>103.56</v>
-      </c>
-      <c r="H59" s="11">
-        <v>39.92</v>
-      </c>
-      <c r="I59" s="11"/>
+      <c r="D59" s="5">
+        <v>2426</v>
+      </c>
+      <c r="E59" s="6">
+        <v>26.4</v>
+      </c>
+      <c r="F59" s="5">
+        <v>363.99</v>
+      </c>
+      <c r="G59" s="5">
+        <v>326.48</v>
+      </c>
+      <c r="H59" s="5">
+        <v>248.07</v>
+      </c>
+      <c r="I59" s="5">
+        <v>209.11</v>
+      </c>
       <c r="J59" s="7">
-        <v>46.4</v>
+        <v>11.5</v>
       </c>
       <c r="K59" s="7">
-        <v>159.4</v>
-      </c>
-      <c r="L59" s="13">
-        <v>3663.6</v>
-      </c>
-      <c r="M59" s="11">
-        <v>276.02999999999997</v>
-      </c>
-      <c r="N59" s="9">
-        <v>3.77</v>
+        <v>31.6</v>
+      </c>
+      <c r="L59" s="8">
+        <v>7821.9</v>
+      </c>
+      <c r="M59" s="5">
+        <v>2463.81</v>
+      </c>
+      <c r="N59" s="15">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C60" s="4" t="s">
+      <c r="A60" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D60" s="11">
+        <v>653.1</v>
+      </c>
+      <c r="E60" s="12">
+        <v>28.9</v>
+      </c>
+      <c r="F60" s="11">
+        <v>216.75</v>
+      </c>
+      <c r="G60" s="11">
+        <v>166.56</v>
+      </c>
+      <c r="H60" s="11">
+        <v>127.17</v>
+      </c>
+      <c r="I60" s="11">
+        <v>76.52</v>
+      </c>
+      <c r="J60" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="K60" s="7">
+        <v>31</v>
+      </c>
+      <c r="L60" s="13">
+        <v>8224.7000000000007</v>
+      </c>
+      <c r="M60" s="11">
+        <v>622.9</v>
+      </c>
+      <c r="N60" s="9">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D60" s="5">
-        <v>1685.6</v>
-      </c>
-      <c r="E60" s="6">
-        <v>29.9</v>
-      </c>
-      <c r="F60" s="5">
-        <v>134.52000000000001</v>
-      </c>
-      <c r="G60" s="5">
-        <v>107.83</v>
-      </c>
-      <c r="H60" s="5">
-        <v>86.26</v>
-      </c>
-      <c r="I60" s="5">
-        <v>81.459999999999994</v>
-      </c>
-      <c r="J60" s="7">
-        <v>24.8</v>
-      </c>
-      <c r="K60" s="7">
-        <v>25</v>
-      </c>
-      <c r="L60" s="8">
-        <v>2806.8</v>
-      </c>
-      <c r="M60" s="5">
-        <v>1839.65</v>
-      </c>
-      <c r="N60" s="9">
-        <v>4.25</v>
-      </c>
-      <c r="O60">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D61" s="11">
-        <v>704.7</v>
-      </c>
-      <c r="E61" s="12">
-        <v>30.7</v>
-      </c>
-      <c r="F61" s="11">
-        <v>61.94</v>
-      </c>
-      <c r="G61" s="11">
-        <v>53.26</v>
-      </c>
-      <c r="H61" s="11">
-        <v>38.71</v>
-      </c>
-      <c r="I61" s="11">
-        <v>28.11</v>
+      <c r="D61" s="5">
+        <v>825.95</v>
+      </c>
+      <c r="E61" s="6">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="F61" s="5">
+        <v>478.7</v>
+      </c>
+      <c r="G61" s="5">
+        <v>229.16</v>
+      </c>
+      <c r="H61" s="5">
+        <v>145.31</v>
+      </c>
+      <c r="I61" s="5">
+        <v>55.42</v>
       </c>
       <c r="J61" s="7">
-        <v>16.3</v>
+        <v>108.9</v>
       </c>
       <c r="K61" s="7">
-        <v>37.6</v>
-      </c>
-      <c r="L61" s="13">
-        <v>1686.7</v>
-      </c>
-      <c r="M61" s="11">
-        <v>798.19</v>
-      </c>
-      <c r="N61" s="9">
-        <v>4.4000000000000004</v>
+        <v>57.7</v>
+      </c>
+      <c r="L61" s="8">
+        <v>8454.2000000000007</v>
+      </c>
+      <c r="M61" s="5">
+        <v>933.56</v>
+      </c>
+      <c r="N61" s="14">
+        <v>13.43</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="C62" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" s="5">
+        <v>283.64999999999998</v>
+      </c>
+      <c r="E62" s="6">
+        <v>27.3</v>
+      </c>
+      <c r="F62" s="5">
+        <v>264.39</v>
+      </c>
+      <c r="G62" s="5">
+        <v>214.27</v>
+      </c>
+      <c r="H62" s="5">
+        <v>44.5</v>
+      </c>
+      <c r="I62" s="5">
+        <v>40.74</v>
+      </c>
+      <c r="J62" s="7">
+        <v>23.4</v>
+      </c>
+      <c r="K62" s="7">
+        <v>381.5</v>
+      </c>
+      <c r="L62" s="8">
+        <v>8524.7000000000007</v>
+      </c>
+      <c r="M62" s="5">
+        <v>318.61</v>
+      </c>
+      <c r="N62" s="9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D62" s="5">
-        <v>206.14</v>
-      </c>
-      <c r="E62" s="6">
-        <v>30.9</v>
-      </c>
-      <c r="F62" s="5">
-        <v>42.23</v>
-      </c>
-      <c r="G62" s="5">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="H62" s="5">
-        <v>25.05</v>
-      </c>
-      <c r="I62" s="5">
-        <v>21.55</v>
-      </c>
-      <c r="J62" s="7">
-        <v>29.1</v>
-      </c>
-      <c r="K62" s="7">
-        <v>30.5</v>
-      </c>
-      <c r="L62" s="8">
-        <v>1287.4000000000001</v>
-      </c>
-      <c r="M62" s="5">
-        <v>202.7</v>
-      </c>
-      <c r="N62" s="9">
-        <v>4.53</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D63" s="11">
-        <v>7.9</v>
-      </c>
-      <c r="E63" s="12">
-        <v>31.6</v>
-      </c>
-      <c r="F63" s="11">
-        <v>42.32</v>
-      </c>
-      <c r="G63" s="11">
-        <v>33.229999999999997</v>
-      </c>
-      <c r="H63" s="11">
-        <v>18.53</v>
-      </c>
-      <c r="I63" s="11">
-        <v>14.52</v>
+      <c r="D63" s="5">
+        <v>183.07</v>
+      </c>
+      <c r="E63" s="6">
+        <v>22.4</v>
+      </c>
+      <c r="F63" s="5">
+        <v>468.72</v>
+      </c>
+      <c r="G63" s="5">
+        <v>387.94</v>
+      </c>
+      <c r="H63" s="5">
+        <v>310.44</v>
+      </c>
+      <c r="I63" s="5">
+        <v>219.04</v>
       </c>
       <c r="J63" s="7">
-        <v>27.4</v>
+        <v>20.8</v>
       </c>
       <c r="K63" s="7">
-        <v>79.3</v>
-      </c>
-      <c r="L63" s="13">
-        <v>338.8</v>
-      </c>
-      <c r="M63" s="11">
-        <v>8.7799999999999994</v>
-      </c>
-      <c r="N63" s="9">
-        <v>4.8499999999999996</v>
+        <v>25</v>
+      </c>
+      <c r="L63" s="8">
+        <v>8908.1</v>
+      </c>
+      <c r="M63" s="5">
+        <v>187.49</v>
+      </c>
+      <c r="N63" s="15">
+        <v>-7.57</v>
+      </c>
+      <c r="O63">
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D64" s="5">
-        <v>1179.5</v>
+        <v>710.85</v>
       </c>
       <c r="E64" s="6">
-        <v>31.7</v>
+        <v>28.8</v>
       </c>
       <c r="F64" s="5">
-        <v>443.74</v>
+        <v>256.13</v>
       </c>
       <c r="G64" s="5">
-        <v>405.25</v>
+        <v>211.19</v>
       </c>
       <c r="H64" s="5">
-        <v>322.98</v>
+        <v>133.29</v>
       </c>
       <c r="I64" s="5">
-        <v>419.16</v>
+        <v>108.58</v>
       </c>
       <c r="J64" s="7">
-        <v>9.5</v>
+        <v>21.3</v>
       </c>
       <c r="K64" s="7">
-        <v>25.5</v>
+        <v>58.4</v>
       </c>
       <c r="L64" s="8">
-        <v>12655.3</v>
+        <v>8939.9</v>
       </c>
       <c r="M64" s="5">
-        <v>1364.46</v>
+        <v>708.65</v>
       </c>
       <c r="N64" s="9">
-        <v>5.21</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="10" t="s">
-        <v>161</v>
+      <c r="A65" s="18" t="s">
+        <v>128</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D65" s="11">
-        <v>427.5</v>
+        <v>677.65</v>
       </c>
       <c r="E65" s="12">
-        <v>31.7</v>
+        <v>27.2</v>
       </c>
       <c r="F65" s="11">
-        <v>42.26</v>
+        <v>250.8</v>
       </c>
       <c r="G65" s="11">
-        <v>21.63</v>
+        <v>167.03</v>
       </c>
       <c r="H65" s="11">
-        <v>8.98</v>
+        <v>140.61000000000001</v>
       </c>
       <c r="I65" s="11">
-        <v>4</v>
+        <v>124.69</v>
       </c>
       <c r="J65" s="7">
-        <v>95.4</v>
+        <v>50.2</v>
       </c>
       <c r="K65" s="7">
-        <v>140.9</v>
+        <v>18.8</v>
       </c>
       <c r="L65" s="13">
-        <v>1176.7</v>
+        <v>9018</v>
       </c>
       <c r="M65" s="11">
-        <v>468.5</v>
+        <v>648.29999999999995</v>
       </c>
       <c r="N65" s="9">
-        <v>5.41</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="18" t="s">
-        <v>163</v>
+      <c r="A66" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D66" s="5">
+        <v>714.1</v>
+      </c>
+      <c r="E66" s="6">
+        <v>34</v>
+      </c>
+      <c r="F66" s="5">
+        <v>605.02</v>
+      </c>
+      <c r="G66" s="5">
+        <v>528.65</v>
+      </c>
+      <c r="H66" s="5">
+        <v>357.14</v>
+      </c>
+      <c r="I66" s="5">
+        <v>278.67</v>
+      </c>
+      <c r="J66" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="K66" s="7">
+        <v>48</v>
+      </c>
+      <c r="L66" s="8">
+        <v>9714.2999999999993</v>
+      </c>
+      <c r="M66" s="5">
+        <v>934.06</v>
+      </c>
+      <c r="N66" s="9">
+        <v>9.11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D66" s="5">
-        <v>482.4</v>
-      </c>
-      <c r="E66" s="6">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="F66" s="5">
-        <v>403.59</v>
-      </c>
-      <c r="G66" s="5">
-        <v>328.68</v>
-      </c>
-      <c r="H66" s="5">
-        <v>233.2</v>
-      </c>
-      <c r="I66" s="5">
-        <v>107.57</v>
-      </c>
-      <c r="J66" s="7">
-        <v>22.8</v>
-      </c>
-      <c r="K66" s="7">
-        <v>40.9</v>
-      </c>
-      <c r="L66" s="8">
-        <v>6312.7</v>
-      </c>
-      <c r="M66" s="5">
-        <v>513.78</v>
-      </c>
-      <c r="N66" s="9">
-        <v>5.64</v>
-      </c>
-      <c r="O66">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D67" s="11">
-        <v>197.34</v>
-      </c>
-      <c r="E67" s="12">
-        <v>33.1</v>
-      </c>
-      <c r="F67" s="11">
-        <v>92.72</v>
-      </c>
-      <c r="G67" s="11">
-        <v>73.81</v>
-      </c>
-      <c r="H67" s="11">
-        <v>45.98</v>
-      </c>
-      <c r="I67" s="11">
-        <v>19.87</v>
+      <c r="D67" s="5">
+        <v>1500.9</v>
+      </c>
+      <c r="E67" s="6">
+        <v>38.1</v>
+      </c>
+      <c r="F67" s="5">
+        <v>378.8</v>
+      </c>
+      <c r="G67" s="5">
+        <v>312.39</v>
+      </c>
+      <c r="H67" s="5">
+        <v>239.19</v>
+      </c>
+      <c r="I67" s="5">
+        <v>201.1</v>
       </c>
       <c r="J67" s="7">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="K67" s="7">
-        <v>60.5</v>
-      </c>
-      <c r="L67" s="13">
-        <v>2206.1999999999998</v>
-      </c>
-      <c r="M67" s="11">
-        <v>187.21</v>
-      </c>
-      <c r="N67" s="9">
-        <v>5.79</v>
+        <v>30.6</v>
+      </c>
+      <c r="L67" s="8">
+        <v>10292.6</v>
+      </c>
+      <c r="M67" s="5">
+        <v>1651.49</v>
+      </c>
+      <c r="N67" s="14">
+        <v>14.96</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
-        <v>167</v>
+      <c r="A68" s="18" t="s">
+        <v>134</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D68" s="5">
-        <v>255.41</v>
+        <v>996.2</v>
       </c>
       <c r="E68" s="6">
-        <v>33.200000000000003</v>
+        <v>27.8</v>
       </c>
       <c r="F68" s="5">
-        <v>92.64</v>
+        <v>448.7</v>
       </c>
       <c r="G68" s="5">
-        <v>77.05</v>
+        <v>378.12</v>
       </c>
       <c r="H68" s="5">
-        <v>45.63</v>
+        <v>271.02999999999997</v>
       </c>
       <c r="I68" s="5">
-        <v>32.89</v>
+        <v>96.61</v>
       </c>
       <c r="J68" s="7">
-        <v>20.2</v>
+        <v>18.7</v>
       </c>
       <c r="K68" s="7">
-        <v>68.8</v>
+        <v>39.5</v>
       </c>
       <c r="L68" s="8">
-        <v>1452.7</v>
+        <v>11641.6</v>
       </c>
       <c r="M68" s="5">
-        <v>305.10000000000002</v>
+        <v>1077.79</v>
       </c>
       <c r="N68" s="9">
-        <v>7.69</v>
+        <v>1</v>
+      </c>
+      <c r="O68">
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D69" s="11">
-        <v>74.38</v>
-      </c>
-      <c r="E69" s="12">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="F69" s="11">
-        <v>7451.1</v>
-      </c>
-      <c r="G69" s="11">
-        <v>6542.91</v>
-      </c>
-      <c r="H69" s="11">
-        <v>5576.05</v>
-      </c>
-      <c r="I69" s="11">
-        <v>5602.14</v>
+      <c r="A69" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" s="5">
+        <v>609.75</v>
+      </c>
+      <c r="E69" s="6">
+        <v>14.5</v>
+      </c>
+      <c r="F69" s="5">
+        <v>297.32</v>
+      </c>
+      <c r="G69" s="5">
+        <v>247.62</v>
+      </c>
+      <c r="H69" s="5">
+        <v>173.77</v>
+      </c>
+      <c r="I69" s="5">
+        <v>122.95</v>
       </c>
       <c r="J69" s="7">
-        <v>13.9</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="K69" s="7">
-        <v>17.3</v>
-      </c>
-      <c r="L69" s="13">
-        <v>65622.100000000006</v>
-      </c>
-      <c r="M69" s="11">
-        <v>81.41</v>
-      </c>
-      <c r="N69" s="9">
-        <v>7.81</v>
+        <v>42.5</v>
+      </c>
+      <c r="L69" s="8">
+        <v>12183.4</v>
+      </c>
+      <c r="M69" s="5">
+        <v>524.4</v>
+      </c>
+      <c r="N69" s="15">
+        <v>-32.78</v>
+      </c>
+      <c r="O69">
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D70" s="5">
-        <v>1037.0999999999999</v>
+        <v>1179.5</v>
       </c>
       <c r="E70" s="6">
-        <v>33.700000000000003</v>
+        <v>31.7</v>
       </c>
       <c r="F70" s="5">
-        <v>412.74</v>
+        <v>443.74</v>
       </c>
       <c r="G70" s="5">
-        <v>375.21</v>
+        <v>405.25</v>
       </c>
       <c r="H70" s="5">
-        <v>362.78</v>
+        <v>322.98</v>
       </c>
       <c r="I70" s="5">
-        <v>290.64</v>
+        <v>419.16</v>
       </c>
       <c r="J70" s="7">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="K70" s="7">
-        <v>3.4</v>
+        <v>25.5</v>
       </c>
       <c r="L70" s="8">
-        <v>7222.1</v>
+        <v>12655.3</v>
       </c>
       <c r="M70" s="5">
-        <v>1131.8399999999999</v>
+        <v>1364.46</v>
       </c>
       <c r="N70" s="9">
-        <v>8.4600000000000009</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D71" s="11">
-        <v>166.28</v>
-      </c>
-      <c r="E71" s="12">
-        <v>33.9</v>
-      </c>
-      <c r="F71" s="11">
-        <v>297.57</v>
-      </c>
-      <c r="G71" s="11">
-        <v>267.61</v>
-      </c>
-      <c r="H71" s="11">
-        <v>219.44</v>
-      </c>
-      <c r="I71" s="11">
-        <v>14.29</v>
+      <c r="A71" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" s="5">
+        <v>379</v>
+      </c>
+      <c r="E71" s="6">
+        <v>37.5</v>
+      </c>
+      <c r="F71" s="5">
+        <v>822.97</v>
+      </c>
+      <c r="G71" s="5">
+        <v>820.31</v>
+      </c>
+      <c r="H71" s="5">
+        <v>797.63</v>
+      </c>
+      <c r="I71" s="5">
+        <v>711.35</v>
       </c>
       <c r="J71" s="7">
-        <v>11.2</v>
+        <v>0.3</v>
       </c>
       <c r="K71" s="7">
-        <v>22</v>
-      </c>
-      <c r="L71" s="13">
-        <v>3604.7</v>
-      </c>
-      <c r="M71" s="11">
-        <v>184.16</v>
-      </c>
-      <c r="N71" s="9">
-        <v>9</v>
-      </c>
-      <c r="O71">
-        <v>30</v>
+        <v>2.8</v>
+      </c>
+      <c r="L71" s="8">
+        <v>14228</v>
+      </c>
+      <c r="M71" s="5">
+        <v>423.16</v>
+      </c>
+      <c r="N71" s="14">
+        <v>12.83</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>176</v>
+        <v>66</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D72" s="5">
-        <v>714.1</v>
+        <v>659.6</v>
       </c>
       <c r="E72" s="6">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="F72" s="5">
+        <v>360.3</v>
+      </c>
+      <c r="G72" s="5">
+        <v>255.4</v>
+      </c>
+      <c r="H72" s="5">
+        <v>227.2</v>
+      </c>
+      <c r="I72" s="5">
+        <v>284.5</v>
+      </c>
+      <c r="J72" s="7">
+        <v>41.1</v>
+      </c>
+      <c r="K72" s="7">
+        <v>12.4</v>
+      </c>
+      <c r="L72" s="8">
+        <v>15640.9</v>
+      </c>
+      <c r="M72" s="5">
+        <v>636.04</v>
+      </c>
+      <c r="N72" s="15">
+        <v>-11.53</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" s="11">
+        <v>156.76</v>
+      </c>
+      <c r="E73" s="12">
+        <v>20</v>
+      </c>
+      <c r="F73" s="11">
+        <v>996.36</v>
+      </c>
+      <c r="G73" s="11">
+        <v>662.14</v>
+      </c>
+      <c r="H73" s="11">
+        <v>99.91</v>
+      </c>
+      <c r="I73" s="11">
+        <v>304.19</v>
+      </c>
+      <c r="J73" s="7">
+        <v>50.5</v>
+      </c>
+      <c r="K73" s="7">
+        <v>562.70000000000005</v>
+      </c>
+      <c r="L73" s="13">
+        <v>15681.7</v>
+      </c>
+      <c r="M73" s="11">
+        <v>145.4</v>
+      </c>
+      <c r="N73" s="15">
+        <v>-9.77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D74" s="11">
+        <v>693.9</v>
+      </c>
+      <c r="E74" s="12">
         <v>34</v>
       </c>
-      <c r="F72" s="5">
-        <v>605.02</v>
-      </c>
-      <c r="G72" s="5">
-        <v>528.65</v>
-      </c>
-      <c r="H72" s="5">
-        <v>357.14</v>
-      </c>
-      <c r="I72" s="5">
-        <v>278.67</v>
-      </c>
-      <c r="J72" s="7">
-        <v>14.4</v>
-      </c>
-      <c r="K72" s="7">
-        <v>48</v>
-      </c>
-      <c r="L72" s="8">
-        <v>9714.2999999999993</v>
-      </c>
-      <c r="M72" s="5">
-        <v>934.06</v>
-      </c>
-      <c r="N72" s="9">
-        <v>9.11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D73" s="11">
-        <v>693.9</v>
-      </c>
-      <c r="E73" s="12">
-        <v>34</v>
-      </c>
-      <c r="F73" s="11">
+      <c r="F74" s="11">
         <v>476.01</v>
       </c>
-      <c r="G73" s="11">
+      <c r="G74" s="11">
         <v>470.19</v>
       </c>
-      <c r="H73" s="11">
+      <c r="H74" s="11">
         <v>353.64</v>
       </c>
-      <c r="I73" s="11">
+      <c r="I74" s="11">
         <v>285.25</v>
       </c>
-      <c r="J73" s="7">
+      <c r="J74" s="7">
         <v>1.2</v>
       </c>
-      <c r="K73" s="7">
+      <c r="K74" s="7">
         <v>33</v>
       </c>
-      <c r="L73" s="13">
+      <c r="L74" s="13">
         <v>16824.099999999999</v>
       </c>
-      <c r="M73" s="11">
+      <c r="M74" s="11">
         <v>743.02</v>
       </c>
-      <c r="N73" s="9">
+      <c r="N74" s="9">
         <v>9.39</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D74" s="5">
-        <v>265.14999999999998</v>
-      </c>
-      <c r="E74" s="6">
-        <v>34.9</v>
-      </c>
-      <c r="F74" s="5">
-        <v>242.01</v>
-      </c>
-      <c r="G74" s="5">
-        <v>180.09</v>
-      </c>
-      <c r="H74" s="5">
-        <v>93.87</v>
-      </c>
-      <c r="I74" s="5">
-        <v>116.06</v>
-      </c>
-      <c r="J74" s="7">
-        <v>34.4</v>
-      </c>
-      <c r="K74" s="7">
-        <v>91.9</v>
-      </c>
-      <c r="L74" s="8">
-        <v>3716.1</v>
-      </c>
-      <c r="M74" s="5">
-        <v>291.56</v>
-      </c>
-      <c r="N74" s="9">
-        <v>9.6999999999999993</v>
-      </c>
-    </row>
     <row r="75" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="18" t="s">
-        <v>182</v>
+      <c r="A75" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>183</v>
+        <v>30</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D75" s="11">
-        <v>502.85</v>
+        <v>2679.7</v>
       </c>
       <c r="E75" s="12">
-        <v>35.4</v>
+        <v>14.2</v>
       </c>
       <c r="F75" s="11">
-        <v>3067.38</v>
+        <v>641.24</v>
       </c>
       <c r="G75" s="11">
-        <v>2540.15</v>
+        <v>536.30999999999995</v>
       </c>
       <c r="H75" s="11">
-        <v>2072.7800000000002</v>
+        <v>457.09</v>
       </c>
       <c r="I75" s="11">
-        <v>1339.71</v>
+        <v>376.26</v>
       </c>
       <c r="J75" s="7">
-        <v>20.8</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="K75" s="7">
-        <v>22.5</v>
+        <v>17.3</v>
       </c>
       <c r="L75" s="13">
-        <v>101963.6</v>
+        <v>19854.3</v>
       </c>
       <c r="M75" s="11">
-        <v>584.94000000000005</v>
-      </c>
-      <c r="N75" s="9">
-        <v>9.77</v>
+        <v>2288.77</v>
+      </c>
+      <c r="N75" s="15">
+        <v>-33.869999999999997</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D76" s="5">
-        <v>114.45</v>
-      </c>
-      <c r="E76" s="6">
-        <v>35.5</v>
-      </c>
-      <c r="F76" s="5">
-        <v>204.3</v>
-      </c>
-      <c r="G76" s="5">
-        <v>133.21</v>
-      </c>
-      <c r="H76" s="5">
-        <v>36.090000000000003</v>
-      </c>
-      <c r="I76" s="5">
-        <v>10.08</v>
+      <c r="A76" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76" s="11">
+        <v>43.88</v>
+      </c>
+      <c r="E76" s="12">
+        <v>22.6</v>
+      </c>
+      <c r="F76" s="11">
+        <v>924.77</v>
+      </c>
+      <c r="G76" s="11">
+        <v>539.12</v>
+      </c>
+      <c r="H76" s="11">
+        <v>228.27</v>
+      </c>
+      <c r="I76" s="11">
+        <v>143.57</v>
       </c>
       <c r="J76" s="7">
-        <v>53.4</v>
+        <v>71.5</v>
       </c>
       <c r="K76" s="7">
-        <v>269.10000000000002</v>
-      </c>
-      <c r="L76" s="8">
-        <v>2330</v>
-      </c>
-      <c r="M76" s="5">
-        <v>134.25</v>
-      </c>
-      <c r="N76" s="14">
-        <v>10.42</v>
+        <v>136.19999999999999</v>
+      </c>
+      <c r="L76" s="13">
+        <v>20209.3</v>
+      </c>
+      <c r="M76" s="11">
+        <v>43.66</v>
+      </c>
+      <c r="N76" s="15">
+        <v>-6.71</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="B77" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="C77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D77" s="11">
-        <v>58.13</v>
-      </c>
-      <c r="E77" s="12">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="F77" s="11">
-        <v>91.7</v>
-      </c>
-      <c r="G77" s="11">
-        <v>77.81</v>
-      </c>
-      <c r="H77" s="11">
-        <v>74.83</v>
-      </c>
-      <c r="I77" s="11">
-        <v>42.84</v>
+      <c r="D77" s="5">
+        <v>1159.8</v>
+      </c>
+      <c r="E77" s="6">
+        <v>12.4</v>
+      </c>
+      <c r="F77" s="5">
+        <v>597.73</v>
+      </c>
+      <c r="G77" s="5">
+        <v>372.78</v>
+      </c>
+      <c r="H77" s="5">
+        <v>273.73</v>
+      </c>
+      <c r="I77" s="5">
+        <v>124.24</v>
       </c>
       <c r="J77" s="7">
-        <v>17.899999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="K77" s="7">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="L77" s="8">
+        <v>20270.900000000001</v>
+      </c>
+      <c r="M77" s="5">
+        <v>1077.01</v>
+      </c>
+      <c r="N77" s="15">
+        <v>-62.94</v>
+      </c>
+      <c r="O77">
         <v>4</v>
       </c>
-      <c r="L77" s="13">
-        <v>1508.8</v>
-      </c>
-      <c r="M77" s="11">
-        <v>71.69</v>
-      </c>
-      <c r="N77" s="14">
-        <v>10.58</v>
-      </c>
     </row>
     <row r="78" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="4" t="s">
-        <v>189</v>
+      <c r="A78" s="19" t="s">
+        <v>126</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D78" s="5">
-        <v>427.45</v>
+        <v>4405</v>
       </c>
       <c r="E78" s="6">
-        <v>36.200000000000003</v>
+        <v>27</v>
       </c>
       <c r="F78" s="5">
-        <v>149.21</v>
+        <v>552.5</v>
       </c>
       <c r="G78" s="5">
-        <v>136.38</v>
+        <v>506.68</v>
       </c>
       <c r="H78" s="5">
-        <v>130.69</v>
+        <v>442.56</v>
       </c>
       <c r="I78" s="5">
-        <v>107.26</v>
+        <v>293.45999999999998</v>
       </c>
       <c r="J78" s="7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="K78" s="7">
-        <v>4.4000000000000004</v>
+        <v>14.5</v>
       </c>
       <c r="L78" s="8">
-        <v>2354.1999999999998</v>
+        <v>20711.900000000001</v>
       </c>
       <c r="M78" s="5">
-        <v>509.27</v>
-      </c>
-      <c r="N78" s="14">
-        <v>11.45</v>
+        <v>3812.6</v>
+      </c>
+      <c r="N78" s="9">
+        <v>0.52</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D79" s="11">
-        <v>167.92</v>
-      </c>
-      <c r="E79" s="12">
-        <v>36.299999999999997</v>
-      </c>
-      <c r="F79" s="11">
-        <v>107.15</v>
-      </c>
-      <c r="G79" s="11">
-        <v>24.79</v>
-      </c>
-      <c r="H79" s="11">
-        <v>17.760000000000002</v>
-      </c>
-      <c r="I79" s="11">
-        <v>45.18</v>
+      <c r="A79" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D79" s="5">
+        <v>608.9</v>
+      </c>
+      <c r="E79" s="6">
+        <v>24.9</v>
+      </c>
+      <c r="F79" s="5">
+        <v>557.02</v>
+      </c>
+      <c r="G79" s="5">
+        <v>425.82</v>
+      </c>
+      <c r="H79" s="5">
+        <v>265.93</v>
+      </c>
+      <c r="I79" s="5">
+        <v>151.12</v>
       </c>
       <c r="J79" s="7">
-        <v>332.3</v>
+        <v>30.8</v>
       </c>
       <c r="K79" s="7">
-        <v>39.6</v>
-      </c>
-      <c r="L79" s="13">
-        <v>1002.4</v>
-      </c>
-      <c r="M79" s="11">
-        <v>173.82</v>
-      </c>
-      <c r="N79" s="14">
-        <v>12.13</v>
+        <v>60.1</v>
+      </c>
+      <c r="L79" s="8">
+        <v>20764.900000000001</v>
+      </c>
+      <c r="M79" s="5">
+        <v>578.76</v>
+      </c>
+      <c r="N79" s="15">
+        <v>-3.64</v>
+      </c>
+      <c r="O79">
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="4" t="s">
-        <v>193</v>
+      <c r="A80" s="18" t="s">
+        <v>73</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D80" s="5">
-        <v>132.6</v>
+        <v>296.5</v>
       </c>
       <c r="E80" s="6">
-        <v>36.700000000000003</v>
+        <v>20</v>
       </c>
       <c r="F80" s="5">
-        <v>119.79</v>
+        <v>1081.55</v>
       </c>
       <c r="G80" s="5">
-        <v>82.18</v>
+        <v>369.01</v>
       </c>
       <c r="H80" s="5">
-        <v>60.17</v>
+        <v>28.9</v>
       </c>
       <c r="I80" s="5">
-        <v>143.24</v>
+        <v>8.94</v>
       </c>
       <c r="J80" s="7">
-        <v>45.8</v>
+        <v>193.1</v>
       </c>
       <c r="K80" s="7">
-        <v>36.6</v>
+        <v>1176.9000000000001</v>
       </c>
       <c r="L80" s="8">
-        <v>1511.5</v>
+        <v>21216.9</v>
       </c>
       <c r="M80" s="5">
-        <v>155.01</v>
-      </c>
-      <c r="N80" s="14">
-        <v>12.67</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D81" s="11">
-        <v>264.8</v>
-      </c>
-      <c r="E81" s="12">
-        <v>37.299999999999997</v>
-      </c>
-      <c r="F81" s="11">
-        <v>376.28</v>
-      </c>
-      <c r="G81" s="11">
-        <v>280.61</v>
-      </c>
-      <c r="H81" s="11">
-        <v>97.67</v>
-      </c>
-      <c r="I81" s="11">
-        <v>34.200000000000003</v>
+        <v>287.33999999999997</v>
+      </c>
+      <c r="N80" s="15">
+        <v>-10.02</v>
+      </c>
+      <c r="O80">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D81" s="5">
+        <v>1140.3</v>
+      </c>
+      <c r="E81" s="6">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F81" s="5">
+        <v>591.17999999999995</v>
+      </c>
+      <c r="G81" s="5">
+        <v>539.1</v>
+      </c>
+      <c r="H81" s="5">
+        <v>521.67999999999995</v>
+      </c>
+      <c r="I81" s="5">
+        <v>494.69</v>
       </c>
       <c r="J81" s="7">
-        <v>34.1</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="K81" s="7">
-        <v>187.3</v>
-      </c>
-      <c r="L81" s="13">
-        <v>3016</v>
-      </c>
-      <c r="M81" s="11">
-        <v>393.9</v>
-      </c>
-      <c r="N81" s="14">
-        <v>12.74</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+        <v>3.3</v>
+      </c>
+      <c r="L81" s="8">
+        <v>23723.5</v>
+      </c>
+      <c r="M81" s="5">
+        <v>1010.63</v>
+      </c>
+      <c r="N81" s="15">
+        <v>-14.03</v>
+      </c>
+      <c r="O81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>198</v>
+        <v>62</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D82" s="5">
-        <v>379</v>
+        <v>246.88</v>
       </c>
       <c r="E82" s="6">
-        <v>37.5</v>
+        <v>17.3</v>
       </c>
       <c r="F82" s="5">
-        <v>822.97</v>
+        <v>949.15</v>
       </c>
       <c r="G82" s="5">
-        <v>820.31</v>
+        <v>478.53</v>
       </c>
       <c r="H82" s="5">
-        <v>797.63</v>
+        <v>279.41000000000003</v>
       </c>
       <c r="I82" s="5">
-        <v>711.35</v>
+        <v>204.65</v>
       </c>
       <c r="J82" s="7">
-        <v>0.3</v>
+        <v>98.3</v>
       </c>
       <c r="K82" s="7">
-        <v>2.8</v>
+        <v>71.3</v>
       </c>
       <c r="L82" s="8">
-        <v>14228</v>
+        <v>24055.8</v>
       </c>
       <c r="M82" s="5">
-        <v>423.16</v>
-      </c>
-      <c r="N82" s="14">
-        <v>12.83</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+        <v>218.36</v>
+      </c>
+      <c r="N82" s="15">
+        <v>-11.79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="10" t="s">
-        <v>199</v>
+        <v>124</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D83" s="11">
-        <v>317.5</v>
+        <v>2516</v>
       </c>
       <c r="E83" s="12">
-        <v>37.700000000000003</v>
+        <v>26.8</v>
       </c>
       <c r="F83" s="11">
-        <v>170.6</v>
+        <v>951.71</v>
       </c>
       <c r="G83" s="11">
-        <v>117.03</v>
+        <v>836.35</v>
       </c>
       <c r="H83" s="11">
-        <v>90.81</v>
+        <v>680.49</v>
       </c>
       <c r="I83" s="11">
-        <v>84.42</v>
+        <v>479.57</v>
       </c>
       <c r="J83" s="7">
-        <v>45.8</v>
+        <v>13.8</v>
       </c>
       <c r="K83" s="7">
-        <v>28.9</v>
+        <v>22.9</v>
       </c>
       <c r="L83" s="13">
-        <v>4689.1000000000004</v>
+        <v>36521.699999999997</v>
       </c>
       <c r="M83" s="11">
-        <v>314.75</v>
-      </c>
-      <c r="N83" s="14">
-        <v>13.06</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="4" t="s">
-        <v>201</v>
+        <v>2677.23</v>
+      </c>
+      <c r="N83" s="9">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="18" t="s">
+        <v>106</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>202</v>
+        <v>107</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D84" s="5">
-        <v>825.95</v>
+        <v>1922.4</v>
       </c>
       <c r="E84" s="6">
-        <v>37.700000000000003</v>
+        <v>24.6</v>
       </c>
       <c r="F84" s="5">
-        <v>478.7</v>
+        <v>924.36</v>
       </c>
       <c r="G84" s="5">
-        <v>229.16</v>
+        <v>681.33</v>
       </c>
       <c r="H84" s="5">
-        <v>145.31</v>
+        <v>498.18</v>
       </c>
       <c r="I84" s="5">
-        <v>55.42</v>
+        <v>532.02</v>
       </c>
       <c r="J84" s="7">
-        <v>108.9</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="K84" s="7">
-        <v>57.7</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="L84" s="8">
-        <v>8454.2000000000007</v>
+        <v>36690</v>
       </c>
       <c r="M84" s="5">
-        <v>933.56</v>
-      </c>
-      <c r="N84" s="14">
-        <v>13.43</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1738.52</v>
+      </c>
+      <c r="N84" s="15">
+        <v>-4.42</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="10" t="s">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>204</v>
+        <v>121</v>
       </c>
       <c r="C85" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D85" s="11">
+        <v>3573.4</v>
+      </c>
+      <c r="E85" s="12">
+        <v>26.7</v>
+      </c>
+      <c r="F85" s="11">
+        <v>1056</v>
+      </c>
+      <c r="G85" s="11">
+        <v>920.39</v>
+      </c>
+      <c r="H85" s="11">
+        <v>816.17</v>
+      </c>
+      <c r="I85" s="11">
+        <v>587.98</v>
+      </c>
+      <c r="J85" s="7">
+        <v>14.7</v>
+      </c>
+      <c r="K85" s="7">
+        <v>12.8</v>
+      </c>
+      <c r="L85" s="13">
+        <v>44810.3</v>
+      </c>
+      <c r="M85" s="11">
+        <v>3150.23</v>
+      </c>
+      <c r="N85" s="15">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D86" s="11">
+        <v>74.38</v>
+      </c>
+      <c r="E86" s="12">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="F86" s="11">
+        <v>7451.1</v>
+      </c>
+      <c r="G86" s="11">
+        <v>6542.91</v>
+      </c>
+      <c r="H86" s="11">
+        <v>5576.05</v>
+      </c>
+      <c r="I86" s="11">
+        <v>5602.14</v>
+      </c>
+      <c r="J86" s="7">
+        <v>13.9</v>
+      </c>
+      <c r="K86" s="7">
+        <v>17.3</v>
+      </c>
+      <c r="L86" s="13">
+        <v>65622.100000000006</v>
+      </c>
+      <c r="M86" s="11">
+        <v>81.41</v>
+      </c>
+      <c r="N86" s="9">
+        <v>7.81</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D85" s="11">
-        <v>1013.05</v>
-      </c>
-      <c r="E85" s="12">
+      <c r="D87" s="5">
+        <v>2398</v>
+      </c>
+      <c r="E87" s="6">
+        <v>39.4</v>
+      </c>
+      <c r="F87" s="5">
+        <v>3711.3</v>
+      </c>
+      <c r="G87" s="5">
+        <v>1867.39</v>
+      </c>
+      <c r="H87" s="5">
+        <v>1237.18</v>
+      </c>
+      <c r="I87" s="5">
+        <v>482.76</v>
+      </c>
+      <c r="J87" s="7">
+        <v>98.7</v>
+      </c>
+      <c r="K87" s="7">
+        <v>50.9</v>
+      </c>
+      <c r="L87" s="8">
+        <v>67310.399999999994</v>
+      </c>
+      <c r="M87" s="5">
+        <v>2868.74</v>
+      </c>
+      <c r="N87" s="14">
+        <v>17.079999999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D88" s="11">
+        <v>502.85</v>
+      </c>
+      <c r="E88" s="12">
+        <v>35.4</v>
+      </c>
+      <c r="F88" s="11">
+        <v>3067.38</v>
+      </c>
+      <c r="G88" s="11">
+        <v>2540.15</v>
+      </c>
+      <c r="H88" s="11">
+        <v>2072.7800000000002</v>
+      </c>
+      <c r="I88" s="11">
+        <v>1339.71</v>
+      </c>
+      <c r="J88" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="K88" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="L88" s="13">
+        <v>101963.6</v>
+      </c>
+      <c r="M88" s="11">
+        <v>584.94000000000005</v>
+      </c>
+      <c r="N88" s="9">
+        <v>9.77</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D89" s="5">
+        <v>378.9</v>
+      </c>
+      <c r="E89" s="6">
+        <v>19.2</v>
+      </c>
+      <c r="F89" s="5">
+        <v>3764.49</v>
+      </c>
+      <c r="G89" s="5">
+        <v>3304.32</v>
+      </c>
+      <c r="H89" s="5">
+        <v>3284.37</v>
+      </c>
+      <c r="I89" s="5">
+        <v>4795.7700000000004</v>
+      </c>
+      <c r="J89" s="7">
+        <v>13.9</v>
+      </c>
+      <c r="K89" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="L89" s="8">
+        <v>102683.6</v>
+      </c>
+      <c r="M89" s="5">
+        <v>369.79</v>
+      </c>
+      <c r="N89" s="15">
+        <v>-10.97</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D90" s="5">
+        <v>5075</v>
+      </c>
+      <c r="E90" s="6">
+        <v>26.7</v>
+      </c>
+      <c r="F90" s="5">
+        <v>5741.73</v>
+      </c>
+      <c r="G90" s="5">
+        <v>4378.4799999999996</v>
+      </c>
+      <c r="H90" s="5">
+        <v>3744.83</v>
+      </c>
+      <c r="I90" s="5">
+        <v>2809.96</v>
+      </c>
+      <c r="J90" s="7">
+        <v>31.1</v>
+      </c>
+      <c r="K90" s="7">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="L90" s="8">
+        <v>103433</v>
+      </c>
+      <c r="M90" s="5">
+        <v>5266.85</v>
+      </c>
+      <c r="N90" s="9">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F85" s="11">
-        <v>84.74</v>
-      </c>
-      <c r="G85" s="11">
-        <v>72.39</v>
-      </c>
-      <c r="H85" s="11">
-        <v>53.83</v>
-      </c>
-      <c r="I85" s="11">
-        <v>33.450000000000003</v>
-      </c>
-      <c r="J85" s="7">
-        <v>17</v>
-      </c>
-      <c r="K85" s="7">
-        <v>34.5</v>
-      </c>
-      <c r="L85" s="13">
-        <v>1203.7</v>
-      </c>
-      <c r="M85" s="11">
-        <v>1122.68</v>
-      </c>
-      <c r="N85" s="14">
-        <v>13.44</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D86" s="5">
-        <v>1500.9</v>
-      </c>
-      <c r="E86" s="6">
-        <v>38.1</v>
-      </c>
-      <c r="F86" s="5">
-        <v>378.8</v>
-      </c>
-      <c r="G86" s="5">
-        <v>312.39</v>
-      </c>
-      <c r="H86" s="5">
-        <v>239.19</v>
-      </c>
-      <c r="I86" s="5">
-        <v>201.1</v>
-      </c>
-      <c r="J86" s="7">
-        <v>21.3</v>
-      </c>
-      <c r="K86" s="7">
-        <v>30.6</v>
-      </c>
-      <c r="L86" s="8">
-        <v>10292.6</v>
-      </c>
-      <c r="M86" s="5">
-        <v>1651.49</v>
-      </c>
-      <c r="N86" s="14">
-        <v>14.96</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="B87" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D87" s="11">
-        <v>124.37</v>
-      </c>
-      <c r="E87" s="12">
-        <v>38.5</v>
-      </c>
-      <c r="F87" s="11">
-        <v>38.840000000000003</v>
-      </c>
-      <c r="G87" s="11">
-        <v>31.74</v>
-      </c>
-      <c r="H87" s="11">
-        <v>18.3</v>
-      </c>
-      <c r="I87" s="11">
-        <v>10.34</v>
-      </c>
-      <c r="J87" s="7">
-        <v>22.4</v>
-      </c>
-      <c r="K87" s="7">
-        <v>73.400000000000006</v>
-      </c>
-      <c r="L87" s="13">
-        <v>739.9</v>
-      </c>
-      <c r="M87" s="11">
+      <c r="B91" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D91" s="5">
+        <v>1135.5999999999999</v>
+      </c>
+      <c r="E91" s="6">
+        <v>14.8</v>
+      </c>
+      <c r="F91" s="5">
+        <v>3428.2</v>
+      </c>
+      <c r="G91" s="5">
+        <v>2764.3</v>
+      </c>
+      <c r="H91" s="5">
+        <v>1549.1</v>
+      </c>
+      <c r="I91" s="5">
+        <v>486.7</v>
+      </c>
+      <c r="J91" s="7">
+        <v>24</v>
+      </c>
+      <c r="K91" s="7">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="L91" s="8">
+        <v>110474.1</v>
+      </c>
+      <c r="M91" s="5">
+        <v>1074.97</v>
+      </c>
+      <c r="N91" s="15">
+        <v>-23.55</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B92" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="N87" s="14">
-        <v>15.54</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D88" s="5">
-        <v>616.04999999999995</v>
-      </c>
-      <c r="E88" s="6">
-        <v>38.5</v>
-      </c>
-      <c r="F88" s="5">
-        <v>212.51</v>
-      </c>
-      <c r="G88" s="5">
-        <v>189.35</v>
-      </c>
-      <c r="H88" s="5">
-        <v>140.97</v>
-      </c>
-      <c r="I88" s="5">
-        <v>97.33</v>
-      </c>
-      <c r="J88" s="7">
-        <v>12.2</v>
-      </c>
-      <c r="K88" s="7">
-        <v>34.299999999999997</v>
-      </c>
-      <c r="L88" s="8">
-        <v>3206.2</v>
-      </c>
-      <c r="M88" s="5">
-        <v>830.14</v>
-      </c>
-      <c r="N88" s="14">
-        <v>16.27</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="B89" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D89" s="11">
-        <v>998.3</v>
-      </c>
-      <c r="E89" s="12">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="F89" s="11">
-        <v>145.72999999999999</v>
-      </c>
-      <c r="G89" s="11">
-        <v>140.91999999999999</v>
-      </c>
-      <c r="H89" s="11">
-        <v>95.51</v>
-      </c>
-      <c r="I89" s="11">
-        <v>124.61</v>
-      </c>
-      <c r="J89" s="7">
-        <v>3.4</v>
-      </c>
-      <c r="K89" s="7">
-        <v>47.5</v>
-      </c>
-      <c r="L89" s="13">
-        <v>1650.8</v>
-      </c>
-      <c r="M89" s="11">
-        <v>1509.5</v>
-      </c>
-      <c r="N89" s="14">
-        <v>16.61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D90" s="5">
-        <v>2398</v>
-      </c>
-      <c r="E90" s="6">
-        <v>39.4</v>
-      </c>
-      <c r="F90" s="5">
-        <v>3711.3</v>
-      </c>
-      <c r="G90" s="5">
-        <v>1867.39</v>
-      </c>
-      <c r="H90" s="5">
-        <v>1237.18</v>
-      </c>
-      <c r="I90" s="5">
-        <v>482.76</v>
-      </c>
-      <c r="J90" s="7">
-        <v>98.7</v>
-      </c>
-      <c r="K90" s="7">
-        <v>50.9</v>
-      </c>
-      <c r="L90" s="8">
-        <v>67310.399999999994</v>
-      </c>
-      <c r="M90" s="5">
-        <v>2868.74</v>
-      </c>
-      <c r="N90" s="14">
-        <v>17.079999999999998</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="B91" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="C91" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D91" s="11">
-        <v>741.75</v>
-      </c>
-      <c r="E91" s="12">
-        <v>39.4</v>
-      </c>
-      <c r="F91" s="11">
-        <v>680.86</v>
-      </c>
-      <c r="G91" s="11">
-        <v>304.38</v>
-      </c>
-      <c r="H91" s="11">
-        <v>31.88</v>
-      </c>
-      <c r="I91" s="11">
-        <v>341.96</v>
-      </c>
-      <c r="J91" s="7">
-        <v>123.7</v>
-      </c>
-      <c r="K91" s="7">
-        <v>854.7</v>
-      </c>
-      <c r="L91" s="13">
-        <v>6432.7</v>
-      </c>
-      <c r="M91" s="11">
-        <v>864.35</v>
-      </c>
-      <c r="N91" s="14">
-        <v>17.559999999999999</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D92" s="5">
-        <v>318.95</v>
-      </c>
-      <c r="E92" s="6">
-        <v>39.700000000000003</v>
-      </c>
-      <c r="F92" s="5">
-        <v>292.76</v>
-      </c>
-      <c r="G92" s="5">
-        <v>230.92</v>
-      </c>
-      <c r="H92" s="5">
-        <v>172.99</v>
-      </c>
-      <c r="I92" s="5">
-        <v>125.08</v>
+      <c r="C92" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" s="11">
+        <v>160</v>
+      </c>
+      <c r="E92" s="12">
+        <v>28.8</v>
+      </c>
+      <c r="F92" s="11">
+        <v>3859.7</v>
+      </c>
+      <c r="G92" s="11">
+        <v>3803</v>
+      </c>
+      <c r="H92" s="11">
+        <v>2716.2</v>
+      </c>
+      <c r="I92" s="11">
+        <v>1495.6</v>
       </c>
       <c r="J92" s="7">
-        <v>26.8</v>
+        <v>1.5</v>
       </c>
       <c r="K92" s="7">
-        <v>33.5</v>
-      </c>
-      <c r="L92" s="8">
-        <v>2004.1</v>
-      </c>
-      <c r="M92" s="5">
-        <v>860.52</v>
-      </c>
-      <c r="N92" s="14">
-        <v>19.27</v>
+        <v>40</v>
+      </c>
+      <c r="L92" s="13">
+        <v>165371.9</v>
+      </c>
+      <c r="M92" s="11">
+        <v>141.05000000000001</v>
+      </c>
+      <c r="N92" s="9">
+        <v>2.95</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N92">
-    <sortCondition ref="E1:E92"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O92">
+    <sortCondition ref="L1:L92"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13070,6 +13070,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
